--- a/genealogia_organizada.xlsx
+++ b/genealogia_organizada.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J670"/>
+  <dimension ref="A1:M670"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,21 @@
           <t>Notas</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Imagen_URL</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Referencias_URLs</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Enlace_Externo</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -511,6 +526,9 @@
           <t>Sentencia 1: Linaje de Adam</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -555,6 +573,9 @@
           <t>Sentencia 1: Linaje de Set</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -599,6 +620,9 @@
           <t>Sentencia 1: Linaje de Enós</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -643,6 +667,9 @@
           <t>Sentencia 1: Linaje de Cainán</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -687,6 +714,9 @@
           <t>Sentencia 1: Linaje de Mahalaleel</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -731,6 +761,9 @@
           <t>Sentencia 1: Linaje de Jared</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -775,6 +808,9 @@
           <t>Sentencia 1: Linaje de Enoc</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -819,6 +855,9 @@
           <t>Sentencia 1: Linaje de Matusalén</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -863,6 +902,9 @@
           <t>Sentencia 1: Linaje de Lamec</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -909,6 +951,9 @@
           <t>Sentencia 1: Hijo de Noé</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -955,6 +1000,9 @@
           <t>Sentencia 1: Hijo de Noé</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1001,6 +1049,9 @@
           <t>Sentencia 1: Hijo de Noé</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1047,6 +1098,9 @@
           <t>Sentencia 2: Hijos de Jafet: Gomer, Magog, Madai, Javán, Tubal, Mesec y Tiras</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1093,6 +1147,9 @@
           <t>Sentencia 2: Hijos de Jafet: Gomer, Magog, Madai, Javán, Tubal, Mesec y Tiras</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1139,6 +1196,9 @@
           <t>Sentencia 2: Hijos de Jafet: Gomer, Magog, Madai, Javán, Tubal, Mesec y Tiras</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1185,6 +1245,9 @@
           <t>Sentencia 2: Hijos de Jafet: Gomer, Magog, Madai, Javán, Tubal, Mesec y Tiras</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1231,6 +1294,9 @@
           <t>Sentencia 2: Hijos de Jafet: Gomer, Magog, Madai, Javán, Tubal, Mesec y Tiras</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1277,6 +1343,9 @@
           <t>Sentencia 2: Hijos de Jafet: Gomer, Magog, Madai, Javán, Tubal, Mesec y Tiras</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1323,6 +1392,9 @@
           <t>Sentencia 2: Hijos de Jafet: Gomer, Magog, Madai, Javán, Tubal, Mesec y Tiras</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1357,6 +1429,9 @@
           <t>Sentencia 3: Hijos de Gomer: Askenaz, Rifat y Togarma</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1391,6 +1466,9 @@
           <t>Sentencia 3: Hijos de Gomer: Askenaz, Rifat y Togarma</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1425,6 +1503,9 @@
           <t>Sentencia 3: Hijos de Gomer: Askenaz, Rifat y Togarma</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1459,6 +1540,9 @@
           <t>Sentencia 4: Hijos de Javán: Elisa, Tarsis, Quitim y Dodanim</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1493,6 +1577,9 @@
           <t>Sentencia 4: Hijos de Javán: Elisa, Tarsis, Quitim y Dodanim</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1527,6 +1614,9 @@
           <t>Sentencia 4: Hijos de Javán: Elisa, Tarsis, Quitim y Dodanim</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1561,6 +1651,9 @@
           <t>Sentencia 4: Hijos de Javán: Elisa, Tarsis, Quitim y Dodanim</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1607,6 +1700,9 @@
           <t>Sentencia 5: Hijos de Cam: Cus, Mizraim, Fut y Canaán</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1653,6 +1749,9 @@
           <t>Sentencia 5: Hijos de Cam: Cus, Mizraim, Fut y Canaán</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1699,6 +1798,9 @@
           <t>Sentencia 5: Hijos de Cam: Cus, Mizraim, Fut y Canaán</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1745,6 +1847,9 @@
           <t>Sentencia 5: Hijos de Cam: Cus, Mizraim, Fut y Canaán</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1779,6 +1884,9 @@
           <t>Sentencia 6: Hijos de Cus: Seba, Havila, Sabta, Raama y Sabteca</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1813,6 +1921,9 @@
           <t>Sentencia 6: Hijos de Cus: Seba, Havila, Sabta, Raama y Sabteca</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1847,6 +1958,9 @@
           <t>Sentencia 6: Hijos de Cus: Seba, Havila, Sabta, Raama y Sabteca</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1881,6 +1995,9 @@
           <t>Sentencia 6: Hijos de Cus: Seba, Havila, Sabta, Raama y Sabteca</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1915,6 +2032,9 @@
           <t>Sentencia 6: Hijos de Cus: Seba, Havila, Sabta, Raama y Sabteca</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1949,6 +2069,9 @@
           <t>Sentencia 7: Hijos de Raama: Seba y Dedán</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1983,6 +2106,9 @@
           <t>Sentencia 7: Hijos de Raama: Seba y Dedán</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2015,6 +2141,9 @@
           <t>Sentencia 8: Cus engendró a Nimrod, quien llegó a ser el primer prepotente  en la tierra</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2061,6 +2190,9 @@
           <t>Sentencia 9: Los hijos de Sem: Elam, Asur, Arfaxad</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2107,6 +2239,9 @@
           <t>Sentencia 9: Los hijos de Sem: Elam, Asur, Arfaxad</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2153,6 +2288,9 @@
           <t>Sentencia 9: Los hijos de Sem: Elam, Asur, Arfaxad</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2197,6 +2335,9 @@
           <t>[Distinción: Cainán post-diluviano, hijo de Arfaxad — Lucas 3:36] Sentencia 10: Arfaxad engendró a Cainán, Cainán engendró a Sala, y Sala engendró a Heber</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2241,6 +2382,9 @@
           <t>Sentencia 10: Arfaxad engendró a Cainán, Cainán engendró a Sala, y Sala engendró a Heber</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2285,6 +2429,9 @@
           <t>Sentencia 10: Arfaxad engendró a Cainán, Cainán engendró a Sala, y Sala engendró a Heber</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2329,6 +2476,9 @@
           <t>Sentencia 11: Heber es padre de Peleg</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2373,6 +2523,9 @@
           <t>Sentencia 11: Peleg es padre de Reu</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2417,6 +2570,9 @@
           <t>Sentencia 11: Reu es padre de Serug</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2461,6 +2617,9 @@
           <t>Sentencia 11: Serug es padre de Nacor</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2505,6 +2664,9 @@
           <t>Sentencia 11: Nacor es padre de Taré</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2549,6 +2711,9 @@
           <t>Sentencia 11: Taré es padre de Abraham</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2595,6 +2760,9 @@
           <t>Sentencia 12: Hijos de Abraham: Isaac e Ismael</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2641,6 +2809,9 @@
           <t>Sentencia 12: Hijos de Abraham: Isaac e Ismael</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2675,6 +2846,9 @@
           <t>Sentencia 15: Los hijos de Jocsán: Seba y Dedán</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2709,6 +2883,9 @@
           <t>Sentencia 15: Los hijos de Jocsán: Seba y Dedán</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2743,6 +2920,9 @@
           <t>Sentencia 16: Hijos de Madián: Efa, Efer, Hanoc, Abida y Elda</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2777,6 +2957,9 @@
           <t>Sentencia 16: Hijos de Madián: Efa, Efer, Hanoc, Abida y Elda</t>
         </is>
       </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2811,6 +2994,9 @@
           <t>Sentencia 16: Hijos de Madián: Efa, Efer, Hanoc, Abida y Elda</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2845,6 +3031,9 @@
           <t>Sentencia 16: Hijos de Madián: Efa, Efer, Hanoc, Abida y Elda</t>
         </is>
       </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2879,6 +3068,9 @@
           <t>Sentencia 16: Hijos de Madián: Efa, Efer, Hanoc, Abida y Elda</t>
         </is>
       </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2925,6 +3117,9 @@
           <t>Sentencia 19: Hijos de Isaac: Esaú e Israel</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2971,6 +3166,9 @@
           <t>Sentencia 19: Hijos de Isaac: Esaú e Israel</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3017,6 +3215,9 @@
           <t>Sentencia 20: Hijos de Esaú: Elifaz, Reuel, Jeús, Jaalam y Coré</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3063,6 +3264,9 @@
           <t>Sentencia 20: Hijos de Esaú: Elifaz, Reuel, Jeús, Jaalam y Coré</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3109,6 +3313,9 @@
           <t>Sentencia 20: Hijos de Esaú: Elifaz, Reuel, Jeús, Jaalam y Coré</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3155,6 +3362,9 @@
           <t>Sentencia 20: Hijos de Esaú: Elifaz, Reuel, Jeús, Jaalam y Coré</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3201,6 +3411,9 @@
           <t>Sentencia 20: Hijos de Esaú: Elifaz, Reuel, Jeús, Jaalam y Coré</t>
         </is>
       </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3235,6 +3448,9 @@
           <t>Sentencia 21: Hijos de Elifaz: Temán, Omar, Zefo, Gatam, Cenaz, y el de Timna, Amalec</t>
         </is>
       </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3269,6 +3485,9 @@
           <t>Sentencia 21: Hijos de Elifaz: Temán, Omar, Zefo, Gatam, Cenaz, y el de Timna, Amalec</t>
         </is>
       </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3303,6 +3522,9 @@
           <t>Sentencia 21: Hijos de Elifaz: Temán, Omar, Zefo, Gatam, Cenaz, y el de Timna, Amalec</t>
         </is>
       </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3337,6 +3559,9 @@
           <t>Sentencia 21: Hijos de Elifaz: Temán, Omar, Zefo, Gatam, Cenaz, y el de Timna, Amalec</t>
         </is>
       </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3371,6 +3596,9 @@
           <t>Sentencia 21: Hijos de Elifaz: Temán, Omar, Zefo, Gatam, Cenaz, y el de Timna, Amalec</t>
         </is>
       </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3405,6 +3633,9 @@
           <t>Sentencia 21: Hijos de Elifaz: Temán, Omar, Zefo, Gatam, Cenaz, y el de Timna, Amalec</t>
         </is>
       </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3439,6 +3670,9 @@
           <t>Sentencia 22: Hijos de Reuel: Nahat, Zera, Sama y Miza</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3473,6 +3707,9 @@
           <t>Sentencia 22: Hijos de Reuel: Nahat, Zera, Sama y Miza</t>
         </is>
       </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3507,6 +3744,9 @@
           <t>Sentencia 22: Hijos de Reuel: Nahat, Zera, Sama y Miza</t>
         </is>
       </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3541,6 +3781,9 @@
           <t>Sentencia 22: Hijos de Reuel: Nahat, Zera, Sama y Miza</t>
         </is>
       </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3575,6 +3818,9 @@
           <t>Sentencia 23: Hijos de Seir: Lotán, Sobal, Zibeón, Aná, Disón, Ezer y Disán</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3609,6 +3855,9 @@
           <t>Sentencia 23: Hijos de Seir: Lotán, Sobal, Zibeón, Aná, Disón, Ezer y Disán</t>
         </is>
       </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3643,6 +3892,9 @@
           <t>Sentencia 23: Hijos de Seir: Lotán, Sobal, Zibeón, Aná, Disón, Ezer y Disán</t>
         </is>
       </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3677,6 +3929,9 @@
           <t>Sentencia 23: Hijos de Seir: Lotán, Sobal, Zibeón, Aná, Disón, Ezer y Disán</t>
         </is>
       </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3711,6 +3966,9 @@
           <t>Sentencia 23: Hijos de Seir: Lotán, Sobal, Zibeón, Aná, Disón, Ezer y Disán</t>
         </is>
       </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3745,6 +4003,9 @@
           <t>Sentencia 23: Hijos de Seir: Lotán, Sobal, Zibeón, Aná, Disón, Ezer y Disán</t>
         </is>
       </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3779,6 +4040,9 @@
           <t>Sentencia 23: Hijos de Seir: Lotán, Sobal, Zibeón, Aná, Disón, Ezer y Disán</t>
         </is>
       </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3813,6 +4077,9 @@
           <t>Sentencia 24: Hijos de Lotán: Hori y Homam; y Timna fue hermana de Lotán</t>
         </is>
       </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3847,6 +4114,9 @@
           <t>Sentencia 24: Hijos de Lotán: Hori y Homam; y Timna fue hermana de Lotán</t>
         </is>
       </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3881,6 +4151,9 @@
           <t>Sentencia 25: Hijos de Sobal: Alván, Manahat, Ebal, Sefo y Onam</t>
         </is>
       </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3915,6 +4188,9 @@
           <t>Sentencia 25: Hijos de Sobal: Alván, Manahat, Ebal, Sefo y Onam</t>
         </is>
       </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3949,6 +4225,9 @@
           <t>Sentencia 25: Hijos de Sobal: Alván, Manahat, Ebal, Sefo y Onam</t>
         </is>
       </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3983,6 +4262,9 @@
           <t>Sentencia 25: Hijos de Sobal: Alván, Manahat, Ebal, Sefo y Onam</t>
         </is>
       </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4017,6 +4299,9 @@
           <t>Sentencia 25: Hijos de Sobal: Alván, Manahat, Ebal, Sefo y Onam</t>
         </is>
       </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4051,6 +4336,9 @@
           <t>Sentencia 26: Hijos de Zibeón: Aja y Aná</t>
         </is>
       </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4085,6 +4373,9 @@
           <t>Sentencia 26: Hijos de Zibeón: Aja y Aná</t>
         </is>
       </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4119,6 +4410,9 @@
           <t>Sentencia 27: Disón fue hijo de Aná; y los hijos de Disón: Amram, Esbán, Itrán y Querán</t>
         </is>
       </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4153,6 +4447,9 @@
           <t>Sentencia 27: Disón fue hijo de Aná; y los hijos de Disón: Amram, Esbán, Itrán y Querán</t>
         </is>
       </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4187,6 +4484,9 @@
           <t>Sentencia 27: Disón fue hijo de Aná; y los hijos de Disón: Amram, Esbán, Itrán y Querán</t>
         </is>
       </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4221,6 +4521,9 @@
           <t>Sentencia 27: Disón fue hijo de Aná; y los hijos de Disón: Amram, Esbán, Itrán y Querán</t>
         </is>
       </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4255,6 +4558,9 @@
           <t>Sentencia 28: Hijos de Ezer: Bilhán, Zaaván y Jaacán</t>
         </is>
       </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4289,6 +4595,9 @@
           <t>Sentencia 28: Hijos de Ezer: Bilhán, Zaaván y Jaacán</t>
         </is>
       </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4323,6 +4632,9 @@
           <t>Sentencia 28: Hijos de Ezer: Bilhán, Zaaván y Jaacán</t>
         </is>
       </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4357,6 +4669,9 @@
           <t>Sentencia 29: Hijos de Disán: Uz y Arán</t>
         </is>
       </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4391,6 +4706,9 @@
           <t>Sentencia 29: Hijos de Disán: Uz y Arán</t>
         </is>
       </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4423,6 +4741,9 @@
           <t>Sentencia 30: Y estos  sus reyes: Bela hijo de Beor, y el nombre de su ciudad era Dinaba</t>
         </is>
       </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4469,6 +4790,9 @@
           <t>Sentencia 40: Estos son los hijos de Israel: Rubén, Simeón, Leví, Judá, Isacar, Zabulón, Dan, José, Benjamín, Neft</t>
         </is>
       </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4515,6 +4839,9 @@
           <t>Sentencia 40: Estos son los hijos de Israel: Rubén, Simeón, Leví, Judá, Isacar, Zabulón, Dan, José, Benjamín, Neft</t>
         </is>
       </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4561,6 +4888,9 @@
           <t>Sentencia 40: Estos son los hijos de Israel: Rubén, Simeón, Leví, Judá, Isacar, Zabulón, Dan, José, Benjamín, Neft</t>
         </is>
       </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4607,6 +4937,9 @@
           <t>Sentencia 40: Estos son los hijos de Israel: Rubén, Simeón, Leví, Judá, Isacar, Zabulón, Dan, José, Benjamín, Neft</t>
         </is>
       </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4653,6 +4986,9 @@
           <t>Sentencia 40: Estos son los hijos de Israel: Rubén, Simeón, Leví, Judá, Isacar, Zabulón, Dan, José, Benjamín, Neft</t>
         </is>
       </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4699,6 +5035,9 @@
           <t>Sentencia 40: Estos son los hijos de Israel: Rubén, Simeón, Leví, Judá, Isacar, Zabulón, Dan, José, Benjamín, Neft</t>
         </is>
       </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4745,6 +5084,9 @@
           <t>Sentencia 40: Estos son los hijos de Israel: Rubén, Simeón, Leví, Judá, Isacar, Zabulón, Dan, José, Benjamín, Neft</t>
         </is>
       </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4791,6 +5133,9 @@
           <t>Sentencia 40: Estos son los hijos de Israel: Rubén, Simeón, Leví, Judá, Isacar, Zabulón, Dan, José, Benjamín, Neft</t>
         </is>
       </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4837,6 +5182,9 @@
           <t>Sentencia 40: Estos son los hijos de Israel: Rubén, Simeón, Leví, Judá, Isacar, Zabulón, Dan, José, Benjamín, Neft</t>
         </is>
       </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4883,6 +5231,9 @@
           <t>Sentencia 40: Estos son los hijos de Israel: Rubén, Simeón, Leví, Judá, Isacar, Zabulón, Dan, José, Benjamín, Neft</t>
         </is>
       </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4929,6 +5280,9 @@
           <t>Sentencia 40: Estos son los hijos de Israel: Rubén, Simeón, Leví, Judá, Isacar, Zabulón, Dan, José, Benjamín, Neft</t>
         </is>
       </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4975,6 +5329,9 @@
           <t>Sentencia 40: Estos son los hijos de Israel: Rubén, Simeón, Leví, Judá, Isacar, Zabulón, Dan, José, Benjamín, Neft</t>
         </is>
       </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5021,6 +5378,9 @@
           <t>Sentencia 41: Hijos de Judá: Er, Onán y Sela</t>
         </is>
       </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5067,6 +5427,9 @@
           <t>Sentencia 41: Hijos de Judá: Er, Onán y Sela</t>
         </is>
       </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5113,6 +5476,9 @@
           <t>Sentencia 41: Hijos de Judá: Er, Onán y Sela</t>
         </is>
       </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5163,6 +5529,9 @@
           <t>Sentencia 44: Y Tamar  su nuera dio a luz a Fares y a Zera</t>
         </is>
       </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5213,6 +5582,9 @@
           <t>Sentencia 44: Y Tamar  su nuera dio a luz a Fares y a Zera</t>
         </is>
       </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5247,6 +5619,9 @@
           <t>Sentencia 46: Hijos de Fares : Hezrón y Hamul</t>
         </is>
       </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5281,6 +5656,9 @@
           <t>Sentencia 46: Hijos de Fares : Hezrón y Hamul</t>
         </is>
       </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5315,6 +5693,9 @@
           <t>Sentencia 47: E hijos de Zera: Zimri, Etán, Hemán, Calcol y Dara: cinco por todos</t>
         </is>
       </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5349,6 +5730,9 @@
           <t>Sentencia 47: E hijos de Zera: Zimri, Etán, Hemán, Calcol y Dara: cinco por todos</t>
         </is>
       </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5383,6 +5767,9 @@
           <t>Sentencia 47: E hijos de Zera: Zimri, Etán, Hemán, Calcol y Dara: cinco por todos</t>
         </is>
       </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5417,6 +5804,9 @@
           <t>Sentencia 47: E hijos de Zera: Zimri, Etán, Hemán, Calcol y Dara: cinco por todos</t>
         </is>
       </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5451,6 +5841,9 @@
           <t>Sentencia 47: E hijos de Zera: Zimri, Etán, Hemán, Calcol y Dara: cinco por todos</t>
         </is>
       </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5483,6 +5876,9 @@
           <t>Sentencia 51: Ram engendró a Aminadab, y Aminadab engendró a Naasón, príncipe de los hijos de Judá</t>
         </is>
       </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5515,6 +5911,9 @@
           <t>Sentencia 51: Ram engendró a Aminadab, y Aminadab engendró a Naasón, príncipe de los hijos de Judá</t>
         </is>
       </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5547,6 +5946,9 @@
           <t>Sentencia 52: Naasón engendró a Salmón, y Salmón engendró a Boaz</t>
         </is>
       </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5579,6 +5981,9 @@
           <t>Sentencia 52: Naasón engendró a Salmón, y Salmón engendró a Boaz</t>
         </is>
       </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5611,6 +6016,9 @@
           <t>Sentencia 53: Boaz engendró a Obed, y Obed engendró a Isaí, e Isaí engendró a Eliab su primogénito, el segundo Abi</t>
         </is>
       </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5643,6 +6051,9 @@
           <t>Sentencia 53: Boaz engendró a Obed, y Obed engendró a Isaí, e Isaí engendró a Eliab su primogénito, el segundo Abi</t>
         </is>
       </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5675,6 +6086,9 @@
           <t>Sentencia 53: Boaz engendró a Obed, y Obed engendró a Isaí, e Isaí engendró a Eliab su primogénito, el segundo Abi</t>
         </is>
       </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5709,6 +6123,9 @@
           <t>Sentencia 54: Los hijos de Sarvia fueron tres: Abisai, Joab y Asael</t>
         </is>
       </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5743,6 +6160,9 @@
           <t>Sentencia 54: Los hijos de Sarvia fueron tres: Abisai, Joab y Asael</t>
         </is>
       </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5777,6 +6197,9 @@
           <t>Sentencia 54: Los hijos de Sarvia fueron tres: Abisai, Joab y Asael</t>
         </is>
       </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5815,6 +6238,9 @@
           <t>Sentencia 55: Abigail dio a luz a Amasa, cuyo padre fue Jeter ismaelita</t>
         </is>
       </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5863,6 +6289,9 @@
           <t>Sentencia 56: Caleb ben Hezrón engendró a Jeriot de su mujer Azuba</t>
         </is>
       </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5895,6 +6324,9 @@
           <t>Sentencia 59: Hur engendró a Uri, y Uri engendró a Bezaleel</t>
         </is>
       </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5927,6 +6359,9 @@
           <t>Sentencia 59: Hur engendró a Uri, y Uri engendró a Bezaleel</t>
         </is>
       </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5959,6 +6394,9 @@
           <t>Sentencia 60: Después Hezrón se llegó a la hija de Maquir, padre de Galaad, a la cual tomó siendo él de sesenta añ</t>
         </is>
       </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5991,6 +6429,9 @@
           <t>Sentencia 61: Segub engendró a Jair, quien poseyó veintitrés ciudades en la tierra de Galaad</t>
         </is>
       </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6023,6 +6464,9 @@
           <t>Sentencia 62: Linaje de Pero Gesur</t>
         </is>
       </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6057,6 +6501,9 @@
           <t>Sentencia 62: Hijo de Aram tomaron Havot-Jair</t>
         </is>
       </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6091,6 +6538,9 @@
           <t>Sentencia 62: Hijo de Aram tomaron Havot-Jair</t>
         </is>
       </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6129,6 +6579,9 @@
           <t>Sentencia 64: Después que murió Hezrón en Caleb-Efrata, Abías mujer de Hezrón dio a luz a Asur, padre de Tecoa</t>
         </is>
       </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6163,6 +6616,9 @@
           <t>Sentencia 68: Hijos de Onam: Samai y Jada</t>
         </is>
       </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6197,6 +6653,9 @@
           <t>Sentencia 68: Hijos de Onam: Samai y Jada</t>
         </is>
       </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6231,6 +6690,9 @@
           <t>Sentencia 69: Hijos de Samai: Nadab y Abisur</t>
         </is>
       </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6265,6 +6727,9 @@
           <t>Sentencia 69: Hijos de Samai: Nadab y Abisur</t>
         </is>
       </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6299,6 +6764,9 @@
           <t>Sentencia 71: Hijos de Nadab: Seled y Apaim</t>
         </is>
       </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6333,6 +6801,9 @@
           <t>Sentencia 71: Hijos de Nadab: Seled y Apaim</t>
         </is>
       </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6369,6 +6840,9 @@
           <t>Sentencia 73: Isi fue hijo de Apaim, y Sesán hijo de Isi, e hijo de Sesán, Ahlai</t>
         </is>
       </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6403,6 +6877,9 @@
           <t>Sentencia 76: Hijos de Jonatán: Pelet y Zaza</t>
         </is>
       </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6437,6 +6914,9 @@
           <t>Sentencia 76: Hijos de Jonatán: Pelet y Zaza</t>
         </is>
       </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6469,6 +6949,9 @@
           <t>Sentencia 80: Atai engendró a Natán, y Natán engendró a Zabad; Zabad engendró a Eflal, Eflal engendró a Obed; Obed</t>
         </is>
       </c>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6501,6 +6984,9 @@
           <t>Sentencia 80: Atai engendró a Natán, y Natán engendró a Zabad; Zabad engendró a Eflal, Eflal engendró a Obed; Obed</t>
         </is>
       </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6533,6 +7019,9 @@
           <t>Sentencia 80: Atai engendró a Natán, y Natán engendró a Zabad; Zabad engendró a Eflal, Eflal engendró a Obed; Obed</t>
         </is>
       </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6565,6 +7054,9 @@
           <t>Sentencia 80: Atai engendró a Natán, y Natán engendró a Zabad; Zabad engendró a Eflal, Eflal engendró a Obed; Obed</t>
         </is>
       </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6597,6 +7089,9 @@
           <t>Sentencia 80: Atai engendró a Natán, y Natán engendró a Zabad; Zabad engendró a Eflal, Eflal engendró a Obed; Obed</t>
         </is>
       </c>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6629,6 +7124,9 @@
           <t>Sentencia 80: Atai engendró a Natán, y Natán engendró a Zabad; Zabad engendró a Eflal, Eflal engendró a Obed; Obed</t>
         </is>
       </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6661,6 +7159,9 @@
           <t>Sentencia 80: Atai engendró a Natán, y Natán engendró a Zabad; Zabad engendró a Eflal, Eflal engendró a Obed; Obed</t>
         </is>
       </c>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6693,6 +7194,9 @@
           <t>Sentencia 81: Hijos de Caleb, hermano de Jerameel: Mesa su primogénito, que fue el padre de Zif; y los hijos de Ma</t>
         </is>
       </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6727,6 +7231,9 @@
           <t>Sentencia 82: Hijos de Hebrón: Coré, Tapúa, Requem y Sema</t>
         </is>
       </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6761,6 +7268,9 @@
           <t>Sentencia 82: Hijos de Hebrón: Coré, Tapúa, Requem y Sema</t>
         </is>
       </c>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6795,6 +7305,9 @@
           <t>Sentencia 82: Hijos de Hebrón: Coré, Tapúa, Requem y Sema</t>
         </is>
       </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6829,6 +7342,9 @@
           <t>Sentencia 82: Hijos de Hebrón: Coré, Tapúa, Requem y Sema</t>
         </is>
       </c>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6861,6 +7377,9 @@
           <t>Sentencia 83: Sema engendró a Raham, padre de Jorcoam, y Requem engendró a Samai</t>
         </is>
       </c>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6893,6 +7412,9 @@
           <t>Sentencia 83: Sema engendró a Raham, padre de Jorcoam, y Requem engendró a Samai</t>
         </is>
       </c>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6929,6 +7451,9 @@
           <t>Sentencia 84: Maón fue hijo de Samai, y Maón padre de Bet-Sur</t>
         </is>
       </c>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -6979,6 +7504,9 @@
           <t>Sentencia 85: Y Efa, concubina de Caleb, dio a luz a Harán, a Mosa y a Gazez</t>
         </is>
       </c>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -7029,6 +7557,9 @@
           <t>Sentencia 85: Y Efa, concubina de Caleb, dio a luz a Harán, a Mosa y a Gazez</t>
         </is>
       </c>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -7079,6 +7610,9 @@
           <t>Sentencia 85: Y Efa, concubina de Caleb, dio a luz a Harán, a Mosa y a Gazez</t>
         </is>
       </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -7111,6 +7645,9 @@
           <t>Sentencia 86: Y Harán engendró a Gazez</t>
         </is>
       </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -7145,6 +7682,9 @@
           <t>Sentencia 87: Hijos de Jahdai: Regem, Jotam, Gesam, Pelet, Efa y Saaf</t>
         </is>
       </c>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -7179,6 +7719,9 @@
           <t>Sentencia 87: Hijos de Jahdai: Regem, Jotam, Gesam, Pelet, Efa y Saaf</t>
         </is>
       </c>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -7213,6 +7756,9 @@
           <t>Sentencia 87: Hijos de Jahdai: Regem, Jotam, Gesam, Pelet, Efa y Saaf</t>
         </is>
       </c>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -7247,6 +7793,9 @@
           <t>Sentencia 87: Hijos de Jahdai: Regem, Jotam, Gesam, Pelet, Efa y Saaf</t>
         </is>
       </c>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -7281,6 +7830,9 @@
           <t>Sentencia 87: Hijos de Jahdai: Regem, Jotam, Gesam, Pelet, Efa y Saaf</t>
         </is>
       </c>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -7315,6 +7867,9 @@
           <t>Sentencia 87: Hijos de Jahdai: Regem, Jotam, Gesam, Pelet, Efa y Saaf</t>
         </is>
       </c>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -7365,6 +7920,9 @@
           <t>Sentencia 88: Maaca, concubina de Caleb, dio a luz a Seber y a Tirhana</t>
         </is>
       </c>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -7415,6 +7973,9 @@
           <t>Sentencia 88: Maaca, concubina de Caleb, dio a luz a Seber y a Tirhana</t>
         </is>
       </c>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -7453,6 +8014,9 @@
           <t>Sentencia 89: También dio a luz a Saaf, padre de Madmana, y a Seva, padre de Macbena, y padre de Gibea; y Acsa fue</t>
         </is>
       </c>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -7499,6 +8063,9 @@
           <t>Sentencia 90: Estos fueron los hijos de Caleb: hijos de Hur, primogénito de Efrata: Sobal, padre de Quiriat-Jearim</t>
         </is>
       </c>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -7545,6 +8112,9 @@
           <t>Sentencia 90: Estos fueron los hijos de Caleb: hijos de Hur, primogénito de Efrata: Sobal, padre de Quiriat-Jearim</t>
         </is>
       </c>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -7591,6 +8161,9 @@
           <t>Sentencia 90: Estos fueron los hijos de Caleb: hijos de Hur, primogénito de Efrata: Sobal, padre de Quiriat-Jearim</t>
         </is>
       </c>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -7623,6 +8196,9 @@
           <t>Sentencia 91: Hijos de Sobal, padre de Quiriat-Jearim: Haroe, la mitad de los manahetitas</t>
         </is>
       </c>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -7655,6 +8231,9 @@
           <t>Sentencia 92: Linaje de Familias de Quiriat-Jearim: los itritas</t>
         </is>
       </c>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -7687,6 +8266,9 @@
           <t>Sentencia 92: Linaje de los futitas</t>
         </is>
       </c>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -7719,6 +8301,9 @@
           <t>Sentencia 92: Linaje de los sumatitas</t>
         </is>
       </c>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -7753,6 +8338,9 @@
           <t>Sentencia 92: Hijo de misraítas</t>
         </is>
       </c>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -7787,6 +8375,9 @@
           <t>Sentencia 92: Hijo de misraítas</t>
         </is>
       </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -7821,6 +8412,9 @@
           <t>Sentencia 93: Hijos de Salma: Bet-Léjem, y los netofatitas, Atrot-Beth-Joab, y Hazi-Hammanahti, zoraíta</t>
         </is>
       </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -7855,6 +8449,9 @@
           <t>Sentencia 93: Hijos de Salma: Bet-Léjem, y los netofatitas, Atrot-Beth-Joab, y Hazi-Hammanahti, zoraíta</t>
         </is>
       </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -7889,6 +8486,9 @@
           <t>Sentencia 93: Hijos de Salma: Bet-Léjem, y los netofatitas, Atrot-Beth-Joab, y Hazi-Hammanahti, zoraíta</t>
         </is>
       </c>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -7923,6 +8523,9 @@
           <t>Sentencia 93: Hijos de Salma: Bet-Léjem, y los netofatitas, Atrot-Beth-Joab, y Hazi-Hammanahti, zoraíta</t>
         </is>
       </c>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -7957,6 +8560,9 @@
           <t>Sentencia 93: Hijos de Salma: Bet-Léjem, y los netofatitas, Atrot-Beth-Joab, y Hazi-Hammanahti, zoraíta</t>
         </is>
       </c>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -7991,6 +8597,9 @@
           <t>Sentencia 94: Y las familias de los escribas que habitaban en Jabes: los tirateos, los simeateos y los sucateos, l</t>
         </is>
       </c>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -8025,6 +8634,9 @@
           <t>Sentencia 94: Y las familias de los escribas que habitaban en Jabes: los tirateos, los simeateos y los sucateos, l</t>
         </is>
       </c>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -8059,6 +8671,9 @@
           <t>Sentencia 94: Y las familias de los escribas que habitaban en Jabes: los tirateos, los simeateos y los sucateos, l</t>
         </is>
       </c>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -8093,6 +8708,9 @@
           <t>Sentencia 94: Y las familias de los escribas que habitaban en Jabes: los tirateos, los simeateos y los sucateos, l</t>
         </is>
       </c>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -8127,6 +8745,9 @@
           <t>Sentencia 94: Y las familias de los escribas que habitaban en Jabes: los tirateos, los simeateos y los sucateos, l</t>
         </is>
       </c>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -8161,6 +8782,9 @@
           <t>Sentencia 95: Estos son los hijos de David que le nacieron en Hebrón: Amnón, el primogénito, de Ahinoam jezreelita</t>
         </is>
       </c>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -8195,6 +8819,9 @@
           <t>Sentencia 95: Estos son los hijos de David que le nacieron en Hebrón: Amnón, el primogénito, de Ahinoam jezreelita</t>
         </is>
       </c>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -8229,6 +8856,9 @@
           <t>Sentencia 95: Estos son los hijos de David que le nacieron en Hebrón: Amnón, el primogénito, de Ahinoam jezreelita</t>
         </is>
       </c>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -8263,6 +8893,9 @@
           <t>Sentencia 95: Estos son los hijos de David que le nacieron en Hebrón: Amnón, el primogénito, de Ahinoam jezreelita</t>
         </is>
       </c>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -8297,6 +8930,9 @@
           <t>Sentencia 95: Estos son los hijos de David que le nacieron en Hebrón: Amnón, el primogénito, de Ahinoam jezreelita</t>
         </is>
       </c>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -8331,6 +8967,9 @@
           <t>Sentencia 95: Estos son los hijos de David que le nacieron en Hebrón: Amnón, el primogénito, de Ahinoam jezreelita</t>
         </is>
       </c>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -8365,6 +9004,9 @@
           <t>Sentencia 95: Estos son los hijos de David que le nacieron en Hebrón: Amnón, el primogénito, de Ahinoam jezreelita</t>
         </is>
       </c>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -8399,6 +9041,9 @@
           <t>Sentencia 95: Estos son los hijos de David que le nacieron en Hebrón: Amnón, el primogénito, de Ahinoam jezreelita</t>
         </is>
       </c>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr"/>
+      <c r="M211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -8433,6 +9078,9 @@
           <t>Sentencia 95: Estos son los hijos de David que le nacieron en Hebrón: Amnón, el primogénito, de Ahinoam jezreelita</t>
         </is>
       </c>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -8467,6 +9115,9 @@
           <t>Sentencia 95: Estos son los hijos de David que le nacieron en Hebrón: Amnón, el primogénito, de Ahinoam jezreelita</t>
         </is>
       </c>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -8501,6 +9152,9 @@
           <t>Sentencia 95: Estos son los hijos de David que le nacieron en Hebrón: Amnón, el primogénito, de Ahinoam jezreelita</t>
         </is>
       </c>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -8535,6 +9189,9 @@
           <t>Sentencia 95: Estos son los hijos de David que le nacieron en Hebrón: Amnón, el primogénito, de Ahinoam jezreelita</t>
         </is>
       </c>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr"/>
+      <c r="M215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -8569,6 +9226,9 @@
           <t>Sentencia 95: Estos son los hijos de David que le nacieron en Hebrón: Amnón, el primogénito, de Ahinoam jezreelita</t>
         </is>
       </c>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr"/>
+      <c r="M216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -8601,6 +9261,9 @@
           <t>Sentencia 99: Linaje de otros nueve: Ibhar</t>
         </is>
       </c>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr"/>
+      <c r="M217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -8635,6 +9298,9 @@
           <t>Sentencia 99: Hijo de Elisama</t>
         </is>
       </c>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr"/>
+      <c r="M218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -8669,6 +9335,9 @@
           <t>Sentencia 99: Hijo de Elisama</t>
         </is>
       </c>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr"/>
+      <c r="M219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -8703,6 +9372,9 @@
           <t>Sentencia 103: Hijos de Josías: Johanán, su primogénito, el segundo Joacim, el tercero Sedequías, el cuarto Salum</t>
         </is>
       </c>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr"/>
+      <c r="M220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -8737,6 +9409,9 @@
           <t>Sentencia 103: Hijos de Josías: Johanán, su primogénito, el segundo Joacim, el tercero Sedequías, el cuarto Salum</t>
         </is>
       </c>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr"/>
+      <c r="M221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -8771,6 +9446,9 @@
           <t>Sentencia 103: Hijos de Josías: Johanán, su primogénito, el segundo Joacim, el tercero Sedequías, el cuarto Salum</t>
         </is>
       </c>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr"/>
+      <c r="M222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -8805,6 +9483,9 @@
           <t>Sentencia 104: Hijos de Joacim: Jeconías su hijo, hijo del cual fue Sedequías</t>
         </is>
       </c>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr"/>
+      <c r="M223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -8839,6 +9520,9 @@
           <t>Sentencia 105: Hijos de Jeconías el cautivo: Salatiel, Malquiram, Pedaías, Senazar, Jecamías, Hosama y Nedabías</t>
         </is>
       </c>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr"/>
+      <c r="M224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -8873,6 +9557,9 @@
           <t>Sentencia 105: Hijos de Jeconías el cautivo: Salatiel, Malquiram, Pedaías, Senazar, Jecamías, Hosama y Nedabías</t>
         </is>
       </c>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr"/>
+      <c r="M225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -8907,6 +9594,9 @@
           <t>Sentencia 105: Hijos de Jeconías el cautivo: Salatiel, Malquiram, Pedaías, Senazar, Jecamías, Hosama y Nedabías</t>
         </is>
       </c>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr"/>
+      <c r="M226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -8941,6 +9631,9 @@
           <t>Sentencia 105: Hijos de Jeconías el cautivo: Salatiel, Malquiram, Pedaías, Senazar, Jecamías, Hosama y Nedabías</t>
         </is>
       </c>
+      <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr"/>
+      <c r="M227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -8975,6 +9668,9 @@
           <t>Sentencia 105: Hijos de Jeconías el cautivo: Salatiel, Malquiram, Pedaías, Senazar, Jecamías, Hosama y Nedabías</t>
         </is>
       </c>
+      <c r="K228" t="inlineStr"/>
+      <c r="L228" t="inlineStr"/>
+      <c r="M228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -9009,6 +9705,9 @@
           <t>Sentencia 105: Hijos de Jeconías el cautivo: Salatiel, Malquiram, Pedaías, Senazar, Jecamías, Hosama y Nedabías</t>
         </is>
       </c>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr"/>
+      <c r="M229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -9043,6 +9742,9 @@
           <t>Sentencia 105: Hijos de Jeconías el cautivo: Salatiel, Malquiram, Pedaías, Senazar, Jecamías, Hosama y Nedabías</t>
         </is>
       </c>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr"/>
+      <c r="M230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -9077,6 +9779,9 @@
           <t>Sentencia 106: Hijos de Pedaías: Zorobabel y Simei</t>
         </is>
       </c>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -9111,6 +9816,9 @@
           <t>Sentencia 106: Hijos de Pedaías: Zorobabel y Simei</t>
         </is>
       </c>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -9145,6 +9853,9 @@
           <t>Sentencia 107: E hijos de Zorobabel: Mesulam, Hananías, y Selomit, su hermana</t>
         </is>
       </c>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr"/>
+      <c r="M233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -9179,6 +9890,9 @@
           <t>Sentencia 107: E hijos de Zorobabel: Mesulam, Hananías, y Selomit, su hermana</t>
         </is>
       </c>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr"/>
+      <c r="M234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -9213,6 +9927,9 @@
           <t>Sentencia 107: E hijos de Zorobabel: Mesulam, Hananías, y Selomit, su hermana</t>
         </is>
       </c>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr"/>
+      <c r="M235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -9245,6 +9962,9 @@
           <t>Sentencia 108: Linaje de También estos cinco: Hasuba</t>
         </is>
       </c>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -9277,6 +9997,9 @@
           <t>Sentencia 108: Linaje de Ohel</t>
         </is>
       </c>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -9311,6 +10034,9 @@
           <t>Sentencia 108: Hijo de Berequías</t>
         </is>
       </c>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
+      <c r="M238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -9345,6 +10071,9 @@
           <t>Sentencia 108: Hijo de Berequías</t>
         </is>
       </c>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -9379,6 +10108,9 @@
           <t>Sentencia 109: E hijos de Hananías: Pelatías y Jesaías; su hijo, Refaías; su hijo, Arnán; su hijo, Abdías; su hijo,</t>
         </is>
       </c>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -9413,6 +10145,9 @@
           <t>Sentencia 109: E hijos de Hananías: Pelatías y Jesaías; su hijo, Refaías; su hijo, Arnán; su hijo, Abdías; su hijo,</t>
         </is>
       </c>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr"/>
+      <c r="M241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -9447,6 +10182,9 @@
           <t>Sentencia 109: E hijos de Hananías: Pelatías y Jesaías; su hijo, Refaías; su hijo, Arnán; su hijo, Abdías; su hijo,</t>
         </is>
       </c>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr"/>
+      <c r="M242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -9481,6 +10219,9 @@
           <t>Sentencia 109: E hijos de Hananías: Pelatías y Jesaías; su hijo, Refaías; su hijo, Arnán; su hijo, Abdías; su hijo,</t>
         </is>
       </c>
+      <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr"/>
+      <c r="M243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -9515,6 +10256,9 @@
           <t>Sentencia 109: E hijos de Hananías: Pelatías y Jesaías; su hijo, Refaías; su hijo, Arnán; su hijo, Abdías; su hijo,</t>
         </is>
       </c>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr"/>
+      <c r="M244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -9549,6 +10293,9 @@
           <t>Sentencia 109: E hijos de Hananías: Pelatías y Jesaías; su hijo, Refaías; su hijo, Arnán; su hijo, Abdías; su hijo,</t>
         </is>
       </c>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -9583,6 +10330,9 @@
           <t>Sentencia 110: Hijo de Secanías fue Semaías; e hijos de Semaías: Hatús, Igal, Barías, Nearías, Sofet y Safat: seis</t>
         </is>
       </c>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr"/>
+      <c r="M246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -9617,6 +10367,9 @@
           <t>Sentencia 110: Hijo de Secanías fue Semaías; e hijos de Semaías: Hatús, Igal, Barías, Nearías, Sofet y Safat: seis</t>
         </is>
       </c>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -9651,6 +10404,9 @@
           <t>Sentencia 110: Hijo de Secanías fue Semaías; e hijos de Semaías: Hatús, Igal, Barías, Nearías, Sofet y Safat: seis</t>
         </is>
       </c>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr"/>
+      <c r="M248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -9685,6 +10441,9 @@
           <t>Sentencia 110: Hijo de Secanías fue Semaías; e hijos de Semaías: Hatús, Igal, Barías, Nearías, Sofet y Safat: seis</t>
         </is>
       </c>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -9719,6 +10478,9 @@
           <t>Sentencia 110: Hijo de Secanías fue Semaías; e hijos de Semaías: Hatús, Igal, Barías, Nearías, Sofet y Safat: seis</t>
         </is>
       </c>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr"/>
+      <c r="M250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -9753,6 +10515,9 @@
           <t>Sentencia 110: Hijo de Secanías fue Semaías; e hijos de Semaías: Hatús, Igal, Barías, Nearías, Sofet y Safat: seis</t>
         </is>
       </c>
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr"/>
+      <c r="M251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -9787,6 +10552,9 @@
           <t>Sentencia 111: Hijos de Nearías fueron estos tres: Elioenai, Ezequías y Azricam</t>
         </is>
       </c>
+      <c r="K252" t="inlineStr"/>
+      <c r="L252" t="inlineStr"/>
+      <c r="M252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -9821,6 +10589,9 @@
           <t>Sentencia 111: Hijos de Nearías fueron estos tres: Elioenai, Ezequías y Azricam</t>
         </is>
       </c>
+      <c r="K253" t="inlineStr"/>
+      <c r="L253" t="inlineStr"/>
+      <c r="M253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -9855,6 +10626,9 @@
           <t>Sentencia 111: Hijos de Nearías fueron estos tres: Elioenai, Ezequías y Azricam</t>
         </is>
       </c>
+      <c r="K254" t="inlineStr"/>
+      <c r="L254" t="inlineStr"/>
+      <c r="M254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -9889,6 +10663,9 @@
           <t>Sentencia 112: Hijos de Elioenai fueron estos siete: Hodavías, Eliasib, Pelaías, Acub, Johanán, Dalaías y Anani</t>
         </is>
       </c>
+      <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr"/>
+      <c r="M255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -9923,6 +10700,9 @@
           <t>Sentencia 112: Hijos de Elioenai fueron estos siete: Hodavías, Eliasib, Pelaías, Acub, Johanán, Dalaías y Anani</t>
         </is>
       </c>
+      <c r="K256" t="inlineStr"/>
+      <c r="L256" t="inlineStr"/>
+      <c r="M256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -9957,6 +10737,9 @@
           <t>Sentencia 112: Hijos de Elioenai fueron estos siete: Hodavías, Eliasib, Pelaías, Acub, Johanán, Dalaías y Anani</t>
         </is>
       </c>
+      <c r="K257" t="inlineStr"/>
+      <c r="L257" t="inlineStr"/>
+      <c r="M257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -9991,6 +10774,9 @@
           <t>Sentencia 112: Hijos de Elioenai fueron estos siete: Hodavías, Eliasib, Pelaías, Acub, Johanán, Dalaías y Anani</t>
         </is>
       </c>
+      <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr"/>
+      <c r="M258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -10025,6 +10811,9 @@
           <t>Sentencia 112: Hijos de Elioenai fueron estos siete: Hodavías, Eliasib, Pelaías, Acub, Johanán, Dalaías y Anani</t>
         </is>
       </c>
+      <c r="K259" t="inlineStr"/>
+      <c r="L259" t="inlineStr"/>
+      <c r="M259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -10059,6 +10848,9 @@
           <t>Sentencia 112: Hijos de Elioenai fueron estos siete: Hodavías, Eliasib, Pelaías, Acub, Johanán, Dalaías y Anani</t>
         </is>
       </c>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr"/>
+      <c r="M260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -10093,6 +10885,9 @@
           <t>Sentencia 112: Hijos de Elioenai fueron estos siete: Hodavías, Eliasib, Pelaías, Acub, Johanán, Dalaías y Anani</t>
         </is>
       </c>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr"/>
+      <c r="M261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -10139,6 +10934,9 @@
           <t>Sentencia 113: Hijos de Judá: Fares, Hezrón, Carmi, Hur y Sobal</t>
         </is>
       </c>
+      <c r="K262" t="inlineStr"/>
+      <c r="L262" t="inlineStr"/>
+      <c r="M262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -10185,6 +10983,9 @@
           <t>Sentencia 113: Hijos de Judá: Fares, Hezrón, Carmi, Hur y Sobal</t>
         </is>
       </c>
+      <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr"/>
+      <c r="M263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -10231,6 +11032,9 @@
           <t>Sentencia 113: Hijos de Judá: Fares, Hezrón, Carmi, Hur y Sobal</t>
         </is>
       </c>
+      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr"/>
+      <c r="M264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -10277,6 +11081,9 @@
           <t>Sentencia 113: Hijos de Judá: Fares, Hezrón, Carmi, Hur y Sobal</t>
         </is>
       </c>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr"/>
+      <c r="M265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -10309,6 +11116,9 @@
           <t>Sentencia 114: Reaía hijo de Sobal engendró a Jahat, y Jahat engendró a Ahumai y a Lahad</t>
         </is>
       </c>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr"/>
+      <c r="M266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -10341,6 +11151,9 @@
           <t>Sentencia 114: Reaía hijo de Sobal engendró a Jahat, y Jahat engendró a Ahumai y a Lahad</t>
         </is>
       </c>
+      <c r="K267" t="inlineStr"/>
+      <c r="L267" t="inlineStr"/>
+      <c r="M267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -10373,6 +11186,9 @@
           <t>Sentencia 116: Linaje de Esta es la estirpe de Etam: Jezreel</t>
         </is>
       </c>
+      <c r="K268" t="inlineStr"/>
+      <c r="L268" t="inlineStr"/>
+      <c r="M268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -10407,6 +11223,9 @@
           <t>Sentencia 116: Hijo de Isma</t>
         </is>
       </c>
+      <c r="K269" t="inlineStr"/>
+      <c r="L269" t="inlineStr"/>
+      <c r="M269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -10441,6 +11260,9 @@
           <t>Sentencia 116: Hijo de Isma</t>
         </is>
       </c>
+      <c r="K270" t="inlineStr"/>
+      <c r="L270" t="inlineStr"/>
+      <c r="M270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -10473,6 +11295,9 @@
           <t>Sentencia 118: Tales fueron los hijos de Hur primogénito de Efrata, padre de Bet-Léjem</t>
         </is>
       </c>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr"/>
+      <c r="M271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -10505,6 +11330,9 @@
           <t>Sentencia 119: Asur, padre de Tecoa, tuvo dos mujeres: Hela y Naara</t>
         </is>
       </c>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -10543,6 +11371,9 @@
           <t>Sentencia 120: Y Naara dio a luz a Ahuzam, Hefer, Temeni y Ahastari</t>
         </is>
       </c>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -10581,6 +11412,9 @@
           <t>Sentencia 120: Y Naara dio a luz a Ahuzam, Hefer, Temeni y Ahastari</t>
         </is>
       </c>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -10619,6 +11453,9 @@
           <t>Sentencia 120: Y Naara dio a luz a Ahuzam, Hefer, Temeni y Ahastari</t>
         </is>
       </c>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -10657,6 +11494,9 @@
           <t>Sentencia 120: Y Naara dio a luz a Ahuzam, Hefer, Temeni y Ahastari</t>
         </is>
       </c>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -10695,6 +11535,9 @@
           <t>Sentencia 122: Los hijos de Hela: Zeret, Jezoar, Etnán y Cos, el cual engendró a Anub, a Zobeba, y la familia de Ah</t>
         </is>
       </c>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -10733,6 +11576,9 @@
           <t>Sentencia 122: Los hijos de Hela: Zeret, Jezoar, Etnán y Cos, el cual engendró a Anub, a Zobeba, y la familia de Ah</t>
         </is>
       </c>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -10771,6 +11617,9 @@
           <t>Sentencia 122: Los hijos de Hela: Zeret, Jezoar, Etnán y Cos, el cual engendró a Anub, a Zobeba, y la familia de Ah</t>
         </is>
       </c>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -10809,6 +11658,9 @@
           <t>Sentencia 122: Los hijos de Hela: Zeret, Jezoar, Etnán y Cos, el cual engendró a Anub, a Zobeba, y la familia de Ah</t>
         </is>
       </c>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -10847,6 +11699,9 @@
           <t>Sentencia 122: Los hijos de Hela: Zeret, Jezoar, Etnán y Cos, el cual engendró a Anub, a Zobeba, y la familia de Ah</t>
         </is>
       </c>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -10885,6 +11740,9 @@
           <t>Sentencia 122: Los hijos de Hela: Zeret, Jezoar, Etnán y Cos, el cual engendró a Anub, a Zobeba, y la familia de Ah</t>
         </is>
       </c>
+      <c r="K282" t="inlineStr"/>
+      <c r="L282" t="inlineStr"/>
+      <c r="M282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -10923,6 +11781,9 @@
           <t>Sentencia 122: Los hijos de Hela: Zeret, Jezoar, Etnán y Cos, el cual engendró a Anub, a Zobeba, y la familia de Ah</t>
         </is>
       </c>
+      <c r="K283" t="inlineStr"/>
+      <c r="L283" t="inlineStr"/>
+      <c r="M283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -10955,6 +11816,9 @@
           <t>Sentencia 124: Linaje de E invocó Jabes al Elohim de Israel diciendo: ¡Oh</t>
         </is>
       </c>
+      <c r="K284" t="inlineStr"/>
+      <c r="L284" t="inlineStr"/>
+      <c r="M284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -10987,6 +11851,9 @@
           <t>Sentencia 124: Linaje de si me dieras bendición</t>
         </is>
       </c>
+      <c r="K285" t="inlineStr"/>
+      <c r="L285" t="inlineStr"/>
+      <c r="M285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -11019,6 +11886,9 @@
           <t>Sentencia 124: Linaje de ensancharas mi territorio</t>
         </is>
       </c>
+      <c r="K286" t="inlineStr"/>
+      <c r="L286" t="inlineStr"/>
+      <c r="M286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -11053,6 +11923,9 @@
           <t>Sentencia 124: Hijo de si tu mano estuviera conmigo</t>
         </is>
       </c>
+      <c r="K287" t="inlineStr"/>
+      <c r="L287" t="inlineStr"/>
+      <c r="M287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -11087,6 +11960,9 @@
           <t>Sentencia 124: Hijo de si tu mano estuviera conmigo</t>
         </is>
       </c>
+      <c r="K288" t="inlineStr"/>
+      <c r="L288" t="inlineStr"/>
+      <c r="M288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -11119,6 +11995,9 @@
           <t>Sentencia 125: Quelub hermano de Súa engendró a Mehir, el cual fue padre de Estón</t>
         </is>
       </c>
+      <c r="K289" t="inlineStr"/>
+      <c r="L289" t="inlineStr"/>
+      <c r="M289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -11151,6 +12030,9 @@
           <t>Sentencia 126: Y Estón engendró a Bet-Rafa, a Paseah, y a Tehina, padre de Ir-Nahas</t>
         </is>
       </c>
+      <c r="K290" t="inlineStr"/>
+      <c r="L290" t="inlineStr"/>
+      <c r="M290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -11185,6 +12067,9 @@
           <t>Sentencia 128: Hijos de Cenaz: Otoniel y Seraías</t>
         </is>
       </c>
+      <c r="K291" t="inlineStr"/>
+      <c r="L291" t="inlineStr"/>
+      <c r="M291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -11219,6 +12104,9 @@
           <t>Sentencia 128: Hijos de Cenaz: Otoniel y Seraías</t>
         </is>
       </c>
+      <c r="K292" t="inlineStr"/>
+      <c r="L292" t="inlineStr"/>
+      <c r="M292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -11253,6 +12141,9 @@
           <t>Sentencia 129: Hijos de Otoniel: Hatat y Meonotai, el cual engendró a Ofra; y Seraías engendró a Joab, padre de los</t>
         </is>
       </c>
+      <c r="K293" t="inlineStr"/>
+      <c r="L293" t="inlineStr"/>
+      <c r="M293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -11287,6 +12178,9 @@
           <t>Sentencia 129: Hijos de Otoniel: Hatat y Meonotai, el cual engendró a Ofra; y Seraías engendró a Joab, padre de los</t>
         </is>
       </c>
+      <c r="K294" t="inlineStr"/>
+      <c r="L294" t="inlineStr"/>
+      <c r="M294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -11321,6 +12215,9 @@
           <t>Sentencia 129: Hijos de Otoniel: Hatat y Meonotai, el cual engendró a Ofra; y Seraías engendró a Joab, padre de los</t>
         </is>
       </c>
+      <c r="K295" t="inlineStr"/>
+      <c r="L295" t="inlineStr"/>
+      <c r="M295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -11355,6 +12252,9 @@
           <t>Sentencia 129: Hijos de Otoniel: Hatat y Meonotai, el cual engendró a Ofra; y Seraías engendró a Joab, padre de los</t>
         </is>
       </c>
+      <c r="K296" t="inlineStr"/>
+      <c r="L296" t="inlineStr"/>
+      <c r="M296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -11389,6 +12289,9 @@
           <t>Sentencia 129: Hijos de Otoniel: Hatat y Meonotai, el cual engendró a Ofra; y Seraías engendró a Joab, padre de los</t>
         </is>
       </c>
+      <c r="K297" t="inlineStr"/>
+      <c r="L297" t="inlineStr"/>
+      <c r="M297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -11435,6 +12338,9 @@
           <t>Sentencia 130: Hijos de Caleb ben Jefone: Iru, Ela y Naam; e hijo de Ela fue Cenaz</t>
         </is>
       </c>
+      <c r="K298" t="inlineStr"/>
+      <c r="L298" t="inlineStr"/>
+      <c r="M298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -11481,6 +12387,9 @@
           <t>Sentencia 130: Hijos de Caleb ben Jefone: Iru, Ela y Naam; e hijo de Ela fue Cenaz</t>
         </is>
       </c>
+      <c r="K299" t="inlineStr"/>
+      <c r="L299" t="inlineStr"/>
+      <c r="M299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -11527,6 +12436,9 @@
           <t>Sentencia 130: Hijos de Caleb ben Jefone: Iru, Ela y Naam; e hijo de Ela fue Cenaz</t>
         </is>
       </c>
+      <c r="K300" t="inlineStr"/>
+      <c r="L300" t="inlineStr"/>
+      <c r="M300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -11573,6 +12485,9 @@
           <t>Sentencia 130: Hijos de Caleb ben Jefone: Iru, Ela y Naam; e hijo de Ela fue Cenaz</t>
         </is>
       </c>
+      <c r="K301" t="inlineStr"/>
+      <c r="L301" t="inlineStr"/>
+      <c r="M301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -11607,6 +12522,9 @@
           <t>Sentencia 132: Hijos de Esdras: Jeter, Mered, Efer y Jalón</t>
         </is>
       </c>
+      <c r="K302" t="inlineStr"/>
+      <c r="L302" t="inlineStr"/>
+      <c r="M302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -11641,6 +12559,9 @@
           <t>Sentencia 132: Hijos de Esdras: Jeter, Mered, Efer y Jalón</t>
         </is>
       </c>
+      <c r="K303" t="inlineStr"/>
+      <c r="L303" t="inlineStr"/>
+      <c r="M303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -11675,6 +12596,9 @@
           <t>Sentencia 132: Hijos de Esdras: Jeter, Mered, Efer y Jalón</t>
         </is>
       </c>
+      <c r="K304" t="inlineStr"/>
+      <c r="L304" t="inlineStr"/>
+      <c r="M304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -11709,6 +12633,9 @@
           <t>Sentencia 132: Hijos de Esdras: Jeter, Mered, Efer y Jalón</t>
         </is>
       </c>
+      <c r="K305" t="inlineStr"/>
+      <c r="L305" t="inlineStr"/>
+      <c r="M305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -11741,6 +12668,9 @@
           <t>Sentencia 133: Y ella concibió a Miriam, a Samai y a Isba, padre de Estemoa</t>
         </is>
       </c>
+      <c r="K306" t="inlineStr"/>
+      <c r="L306" t="inlineStr"/>
+      <c r="M306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -11779,6 +12709,9 @@
           <t>Sentencia 134: Y su mujer Jehudaía dio a luz a Jered padre de Gedor, a Heber padre de Soco y a Jecutiel padre de Za</t>
         </is>
       </c>
+      <c r="K307" t="inlineStr"/>
+      <c r="L307" t="inlineStr"/>
+      <c r="M307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -11813,6 +12746,9 @@
           <t>Sentencia 137: Hijos de Simón: Amnón, Rina, Ben-Hanán y Tilón</t>
         </is>
       </c>
+      <c r="K308" t="inlineStr"/>
+      <c r="L308" t="inlineStr"/>
+      <c r="M308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -11847,6 +12783,9 @@
           <t>Sentencia 137: Hijos de Simón: Amnón, Rina, Ben-Hanán y Tilón</t>
         </is>
       </c>
+      <c r="K309" t="inlineStr"/>
+      <c r="L309" t="inlineStr"/>
+      <c r="M309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -11881,6 +12820,9 @@
           <t>Sentencia 137: Hijos de Simón: Amnón, Rina, Ben-Hanán y Tilón</t>
         </is>
       </c>
+      <c r="K310" t="inlineStr"/>
+      <c r="L310" t="inlineStr"/>
+      <c r="M310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -11915,6 +12857,9 @@
           <t>Sentencia 138: Hijos de Isi: Zohet y Benzohet</t>
         </is>
       </c>
+      <c r="K311" t="inlineStr"/>
+      <c r="L311" t="inlineStr"/>
+      <c r="M311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -11949,6 +12894,9 @@
           <t>Sentencia 138: Hijos de Isi: Zohet y Benzohet</t>
         </is>
       </c>
+      <c r="K312" t="inlineStr"/>
+      <c r="L312" t="inlineStr"/>
+      <c r="M312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -11983,6 +12931,9 @@
           <t>Sentencia 139: Hijos de Sela ben Judá: Er, padre de Leca, y Laada, padre de Maresa, y las familias de los que traba</t>
         </is>
       </c>
+      <c r="K313" t="inlineStr"/>
+      <c r="L313" t="inlineStr"/>
+      <c r="M313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -12017,6 +12968,9 @@
           <t>Sentencia 139: Hijos de Sela ben Judá: Er, padre de Leca, y Laada, padre de Maresa, y las familias de los que traba</t>
         </is>
       </c>
+      <c r="K314" t="inlineStr"/>
+      <c r="L314" t="inlineStr"/>
+      <c r="M314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -12051,6 +13005,9 @@
           <t>Sentencia 139: Hijos de Sela ben Judá: Er, padre de Leca, y Laada, padre de Maresa, y las familias de los que traba</t>
         </is>
       </c>
+      <c r="K315" t="inlineStr"/>
+      <c r="L315" t="inlineStr"/>
+      <c r="M315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -12085,6 +13042,9 @@
           <t>Sentencia 139: Hijos de Sela ben Judá: Er, padre de Leca, y Laada, padre de Maresa, y las familias de los que traba</t>
         </is>
       </c>
+      <c r="K316" t="inlineStr"/>
+      <c r="L316" t="inlineStr"/>
+      <c r="M316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -12119,6 +13079,9 @@
           <t>Sentencia 139: Hijos de Sela ben Judá: Er, padre de Leca, y Laada, padre de Maresa, y las familias de los que traba</t>
         </is>
       </c>
+      <c r="K317" t="inlineStr"/>
+      <c r="L317" t="inlineStr"/>
+      <c r="M317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -12153,6 +13116,9 @@
           <t>Sentencia 139: Hijos de Sela ben Judá: Er, padre de Leca, y Laada, padre de Maresa, y las familias de los que traba</t>
         </is>
       </c>
+      <c r="K318" t="inlineStr"/>
+      <c r="L318" t="inlineStr"/>
+      <c r="M318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -12187,6 +13153,9 @@
           <t>Sentencia 139: Hijos de Sela ben Judá: Er, padre de Leca, y Laada, padre de Maresa, y las familias de los que traba</t>
         </is>
       </c>
+      <c r="K319" t="inlineStr"/>
+      <c r="L319" t="inlineStr"/>
+      <c r="M319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -12221,6 +13190,9 @@
           <t>Sentencia 139: Hijos de Sela ben Judá: Er, padre de Leca, y Laada, padre de Maresa, y las familias de los que traba</t>
         </is>
       </c>
+      <c r="K320" t="inlineStr"/>
+      <c r="L320" t="inlineStr"/>
+      <c r="M320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -12255,6 +13227,9 @@
           <t>Sentencia 139: Hijos de Sela ben Judá: Er, padre de Leca, y Laada, padre de Maresa, y las familias de los que traba</t>
         </is>
       </c>
+      <c r="K321" t="inlineStr"/>
+      <c r="L321" t="inlineStr"/>
+      <c r="M321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -12289,6 +13264,9 @@
           <t>Sentencia 139: Hijos de Sela ben Judá: Er, padre de Leca, y Laada, padre de Maresa, y las familias de los que traba</t>
         </is>
       </c>
+      <c r="K322" t="inlineStr"/>
+      <c r="L322" t="inlineStr"/>
+      <c r="M322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -12321,6 +13299,9 @@
           <t>Sentencia 140: Linaje de Estos eran alfareros</t>
         </is>
       </c>
+      <c r="K323" t="inlineStr"/>
+      <c r="L323" t="inlineStr"/>
+      <c r="M323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -12353,6 +13334,9 @@
           <t>Sentencia 140: Linaje de habitaban en medio de plantíos</t>
         </is>
       </c>
+      <c r="K324" t="inlineStr"/>
+      <c r="L324" t="inlineStr"/>
+      <c r="M324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -12387,6 +13371,9 @@
           <t>Sentencia 140: Hijo de cercados</t>
         </is>
       </c>
+      <c r="K325" t="inlineStr"/>
+      <c r="L325" t="inlineStr"/>
+      <c r="M325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -12421,6 +13408,9 @@
           <t>Sentencia 140: Hijo de cercados</t>
         </is>
       </c>
+      <c r="K326" t="inlineStr"/>
+      <c r="L326" t="inlineStr"/>
+      <c r="M326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -12467,6 +13457,9 @@
           <t>Sentencia 141: Hijos de Simeón: Nemuel, Jamín, Jarib, Zera, Saúl, y Salum su hijo, Mibsam su hijo y Misma su hijo</t>
         </is>
       </c>
+      <c r="K327" t="inlineStr"/>
+      <c r="L327" t="inlineStr"/>
+      <c r="M327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -12513,6 +13506,9 @@
           <t>Sentencia 141: Hijos de Simeón: Nemuel, Jamín, Jarib, Zera, Saúl, y Salum su hijo, Mibsam su hijo y Misma su hijo</t>
         </is>
       </c>
+      <c r="K328" t="inlineStr"/>
+      <c r="L328" t="inlineStr"/>
+      <c r="M328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -12559,6 +13555,9 @@
           <t>Sentencia 141: Hijos de Simeón: Nemuel, Jamín, Jarib, Zera, Saúl, y Salum su hijo, Mibsam su hijo y Misma su hijo</t>
         </is>
       </c>
+      <c r="K329" t="inlineStr"/>
+      <c r="L329" t="inlineStr"/>
+      <c r="M329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -12605,6 +13604,9 @@
           <t>Sentencia 141: Hijos de Simeón: Nemuel, Jamín, Jarib, Zera, Saúl, y Salum su hijo, Mibsam su hijo y Misma su hijo</t>
         </is>
       </c>
+      <c r="K330" t="inlineStr"/>
+      <c r="L330" t="inlineStr"/>
+      <c r="M330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -12651,6 +13653,9 @@
           <t>Sentencia 141: Hijos de Simeón: Nemuel, Jamín, Jarib, Zera, Saúl, y Salum su hijo, Mibsam su hijo y Misma su hijo</t>
         </is>
       </c>
+      <c r="K331" t="inlineStr"/>
+      <c r="L331" t="inlineStr"/>
+      <c r="M331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -12697,6 +13702,9 @@
           <t>Sentencia 141: Hijos de Simeón: Nemuel, Jamín, Jarib, Zera, Saúl, y Salum su hijo, Mibsam su hijo y Misma su hijo</t>
         </is>
       </c>
+      <c r="K332" t="inlineStr"/>
+      <c r="L332" t="inlineStr"/>
+      <c r="M332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -12743,6 +13751,9 @@
           <t>Sentencia 141: Hijos de Simeón: Nemuel, Jamín, Jarib, Zera, Saúl, y Salum su hijo, Mibsam su hijo y Misma su hijo</t>
         </is>
       </c>
+      <c r="K333" t="inlineStr"/>
+      <c r="L333" t="inlineStr"/>
+      <c r="M333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -12789,6 +13800,9 @@
           <t>Sentencia 141: Hijos de Simeón: Nemuel, Jamín, Jarib, Zera, Saúl, y Salum su hijo, Mibsam su hijo y Misma su hijo</t>
         </is>
       </c>
+      <c r="K334" t="inlineStr"/>
+      <c r="L334" t="inlineStr"/>
+      <c r="M334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -12823,6 +13837,9 @@
           <t>Sentencia 142: Hijos de Misma: Hamuel su hijo, Zacur su hijo, y Simei su hijo</t>
         </is>
       </c>
+      <c r="K335" t="inlineStr"/>
+      <c r="L335" t="inlineStr"/>
+      <c r="M335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -12857,6 +13874,9 @@
           <t>Sentencia 142: Hijos de Misma: Hamuel su hijo, Zacur su hijo, y Simei su hijo</t>
         </is>
       </c>
+      <c r="K336" t="inlineStr"/>
+      <c r="L336" t="inlineStr"/>
+      <c r="M336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -12891,6 +13911,9 @@
           <t>Sentencia 142: Hijos de Misma: Hamuel su hijo, Zacur su hijo, y Simei su hijo</t>
         </is>
       </c>
+      <c r="K337" t="inlineStr"/>
+      <c r="L337" t="inlineStr"/>
+      <c r="M337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -12925,6 +13948,9 @@
           <t>Sentencia 146: Hijo de Estas son las moradas de ellos</t>
         </is>
       </c>
+      <c r="K338" t="inlineStr"/>
+      <c r="L338" t="inlineStr"/>
+      <c r="M338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -12959,6 +13985,9 @@
           <t>Sentencia 149: Hijo de llegaron hasta la entrada de Gedor hasta el oriente del valle</t>
         </is>
       </c>
+      <c r="K339" t="inlineStr"/>
+      <c r="L339" t="inlineStr"/>
+      <c r="M339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -12991,6 +14020,9 @@
           <t>Sentencia 150: Linaje de hallaron pastos buenos</t>
         </is>
       </c>
+      <c r="K340" t="inlineStr"/>
+      <c r="L340" t="inlineStr"/>
+      <c r="M340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -13023,6 +14055,9 @@
           <t>Sentencia 150: Linaje de abundantes</t>
         </is>
       </c>
+      <c r="K341" t="inlineStr"/>
+      <c r="L341" t="inlineStr"/>
+      <c r="M341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -13055,6 +14090,9 @@
           <t>Sentencia 150: Linaje de tierra era muy espaciosa</t>
         </is>
       </c>
+      <c r="K342" t="inlineStr"/>
+      <c r="L342" t="inlineStr"/>
+      <c r="M342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -13089,6 +14127,9 @@
           <t>Sentencia 150: Hijo de tranquila</t>
         </is>
       </c>
+      <c r="K343" t="inlineStr"/>
+      <c r="L343" t="inlineStr"/>
+      <c r="M343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -13123,6 +14164,9 @@
           <t>Sentencia 150: Hijo de tranquila</t>
         </is>
       </c>
+      <c r="K344" t="inlineStr"/>
+      <c r="L344" t="inlineStr"/>
+      <c r="M344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -13155,6 +14199,9 @@
           <t>Sentencia 151: Linaje de estos que han sido escritos por sus nombres</t>
         </is>
       </c>
+      <c r="K345" t="inlineStr"/>
+      <c r="L345" t="inlineStr"/>
+      <c r="M345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -13187,6 +14234,9 @@
           <t>Sentencia 151: Linaje de vinieron en días de Ezequías rey de Judá</t>
         </is>
       </c>
+      <c r="K346" t="inlineStr"/>
+      <c r="L346" t="inlineStr"/>
+      <c r="M346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -13219,6 +14269,9 @@
           <t>Sentencia 151: Linaje de destruyeron las tiendas</t>
         </is>
       </c>
+      <c r="K347" t="inlineStr"/>
+      <c r="L347" t="inlineStr"/>
+      <c r="M347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -13251,6 +14304,9 @@
           <t>Sentencia 151: Linaje de cabañas que hallaron allí</t>
         </is>
       </c>
+      <c r="K348" t="inlineStr"/>
+      <c r="L348" t="inlineStr"/>
+      <c r="M348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -13285,6 +14341,9 @@
           <t>Sentencia 151: Hijo de dedicaron al exterminio hasta hoy</t>
         </is>
       </c>
+      <c r="K349" t="inlineStr"/>
+      <c r="L349" t="inlineStr"/>
+      <c r="M349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -13319,6 +14378,9 @@
           <t>Sentencia 151: Hijo de dedicaron al exterminio hasta hoy</t>
         </is>
       </c>
+      <c r="K350" t="inlineStr"/>
+      <c r="L350" t="inlineStr"/>
+      <c r="M350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -13353,6 +14415,9 @@
           <t>Sentencia 155: Hijos de Joel: Semaías su hijo, Gog su hijo, Simei su hijo, Micaía su hijo, Reaía su hijo, Baal su h</t>
         </is>
       </c>
+      <c r="K351" t="inlineStr"/>
+      <c r="L351" t="inlineStr"/>
+      <c r="M351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -13387,6 +14452,9 @@
           <t>Sentencia 155: Hijos de Joel: Semaías su hijo, Gog su hijo, Simei su hijo, Micaía su hijo, Reaía su hijo, Baal su h</t>
         </is>
       </c>
+      <c r="K352" t="inlineStr"/>
+      <c r="L352" t="inlineStr"/>
+      <c r="M352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -13421,6 +14489,9 @@
           <t>Sentencia 155: Hijos de Joel: Semaías su hijo, Gog su hijo, Simei su hijo, Micaía su hijo, Reaía su hijo, Baal su h</t>
         </is>
       </c>
+      <c r="K353" t="inlineStr"/>
+      <c r="L353" t="inlineStr"/>
+      <c r="M353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -13455,6 +14526,9 @@
           <t>Sentencia 155: Hijos de Joel: Semaías su hijo, Gog su hijo, Simei su hijo, Micaía su hijo, Reaía su hijo, Baal su h</t>
         </is>
       </c>
+      <c r="K354" t="inlineStr"/>
+      <c r="L354" t="inlineStr"/>
+      <c r="M354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -13489,6 +14563,9 @@
           <t>Sentencia 155: Hijos de Joel: Semaías su hijo, Gog su hijo, Simei su hijo, Micaía su hijo, Reaía su hijo, Baal su h</t>
         </is>
       </c>
+      <c r="K355" t="inlineStr"/>
+      <c r="L355" t="inlineStr"/>
+      <c r="M355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -13523,6 +14600,9 @@
           <t>Sentencia 155: Hijos de Joel: Semaías su hijo, Gog su hijo, Simei su hijo, Micaía su hijo, Reaía su hijo, Baal su h</t>
         </is>
       </c>
+      <c r="K356" t="inlineStr"/>
+      <c r="L356" t="inlineStr"/>
+      <c r="M356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -13557,6 +14637,9 @@
           <t>Sentencia 155: Hijos de Joel: Semaías su hijo, Gog su hijo, Simei su hijo, Micaía su hijo, Reaía su hijo, Baal su h</t>
         </is>
       </c>
+      <c r="K357" t="inlineStr"/>
+      <c r="L357" t="inlineStr"/>
+      <c r="M357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -13591,6 +14674,9 @@
           <t>Sentencia 155: Hijos de Joel: Semaías su hijo, Gog su hijo, Simei su hijo, Micaía su hijo, Reaía su hijo, Baal su h</t>
         </is>
       </c>
+      <c r="K358" t="inlineStr"/>
+      <c r="L358" t="inlineStr"/>
+      <c r="M358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -13625,6 +14711,9 @@
           <t>Sentencia 155: Hijos de Joel: Semaías su hijo, Gog su hijo, Simei su hijo, Micaía su hijo, Reaía su hijo, Baal su h</t>
         </is>
       </c>
+      <c r="K359" t="inlineStr"/>
+      <c r="L359" t="inlineStr"/>
+      <c r="M359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -13657,6 +14746,9 @@
           <t>Sentencia 158: Habitó también desde el oriente hasta la entrada del desierto es padre de desde el río Éufrates</t>
         </is>
       </c>
+      <c r="K360" t="inlineStr"/>
+      <c r="L360" t="inlineStr"/>
+      <c r="M360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -13689,6 +14781,9 @@
           <t>Sentencia 158: desde el río Éufrates es padre de porque tenía mucho ganado en la tierra de Galaad</t>
         </is>
       </c>
+      <c r="K361" t="inlineStr"/>
+      <c r="L361" t="inlineStr"/>
+      <c r="M361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -13723,6 +14818,9 @@
           <t>Sentencia 159: Hijo de Pero en tiempo de Saúl hicieron guerra contra los agarenos</t>
         </is>
       </c>
+      <c r="K362" t="inlineStr"/>
+      <c r="L362" t="inlineStr"/>
+      <c r="M362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -13757,6 +14855,9 @@
           <t>Sentencia 159: Hijo de Pero en tiempo de Saúl hicieron guerra contra los agarenos</t>
         </is>
       </c>
+      <c r="K363" t="inlineStr"/>
+      <c r="L363" t="inlineStr"/>
+      <c r="M363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -13789,6 +14890,9 @@
           <t>Sentencia 165: Linaje de habitaron en Galaad</t>
         </is>
       </c>
+      <c r="K364" t="inlineStr"/>
+      <c r="L364" t="inlineStr"/>
+      <c r="M364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -13823,6 +14927,9 @@
           <t>Sentencia 165: Hijo de en Basán</t>
         </is>
       </c>
+      <c r="K365" t="inlineStr"/>
+      <c r="L365" t="inlineStr"/>
+      <c r="M365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -13857,6 +14964,9 @@
           <t>Sentencia 165: Hijo de en Basán</t>
         </is>
       </c>
+      <c r="K366" t="inlineStr"/>
+      <c r="L366" t="inlineStr"/>
+      <c r="M366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -13889,6 +14999,9 @@
           <t>Sentencia 168: Linaje de Estos tuvieron guerra contra los agarenos</t>
         </is>
       </c>
+      <c r="K367" t="inlineStr"/>
+      <c r="L367" t="inlineStr"/>
+      <c r="M367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -13923,6 +15036,9 @@
           <t>Sentencia 168: Hijo de Jetur</t>
         </is>
       </c>
+      <c r="K368" t="inlineStr"/>
+      <c r="L368" t="inlineStr"/>
+      <c r="M368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -13957,6 +15073,9 @@
           <t>Sentencia 168: Hijo de Jetur</t>
         </is>
       </c>
+      <c r="K369" t="inlineStr"/>
+      <c r="L369" t="inlineStr"/>
+      <c r="M369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -13989,6 +15108,9 @@
           <t>Sentencia 170: Linaje de tomaron sus ganados: cincuenta mil camellos</t>
         </is>
       </c>
+      <c r="K370" t="inlineStr"/>
+      <c r="L370" t="inlineStr"/>
+      <c r="M370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -14023,6 +15145,9 @@
           <t>Sentencia 170: Hijo de doscientas cincuenta mil ovejas</t>
         </is>
       </c>
+      <c r="K371" t="inlineStr"/>
+      <c r="L371" t="inlineStr"/>
+      <c r="M371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -14057,6 +15182,9 @@
           <t>Sentencia 170: Hijo de doscientas cincuenta mil ovejas</t>
         </is>
       </c>
+      <c r="K372" t="inlineStr"/>
+      <c r="L372" t="inlineStr"/>
+      <c r="M372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -14089,6 +15217,9 @@
           <t>Sentencia 171: Muchos es padre de pues</t>
         </is>
       </c>
+      <c r="K373" t="inlineStr"/>
+      <c r="L373" t="inlineStr"/>
+      <c r="M373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -14121,6 +15252,9 @@
           <t>Sentencia 171: pues es padre de cayeron muertos</t>
         </is>
       </c>
+      <c r="K374" t="inlineStr"/>
+      <c r="L374" t="inlineStr"/>
+      <c r="M374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -14153,6 +15287,9 @@
           <t>Sentencia 171: cayeron muertos es padre de porque la batalla era de Ha-Elohim</t>
         </is>
       </c>
+      <c r="K375" t="inlineStr"/>
+      <c r="L375" t="inlineStr"/>
+      <c r="M375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -14185,6 +15322,9 @@
           <t>Sentencia 174: Linaje de Estos son los jefes de las casas de sus padres: Efer</t>
         </is>
       </c>
+      <c r="K376" t="inlineStr"/>
+      <c r="L376" t="inlineStr"/>
+      <c r="M376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -14217,6 +15357,9 @@
           <t>Sentencia 174: Linaje de Isi</t>
         </is>
       </c>
+      <c r="K377" t="inlineStr"/>
+      <c r="L377" t="inlineStr"/>
+      <c r="M377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -14249,6 +15392,9 @@
           <t>Sentencia 174: Linaje de Eliel</t>
         </is>
       </c>
+      <c r="K378" t="inlineStr"/>
+      <c r="L378" t="inlineStr"/>
+      <c r="M378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -14281,6 +15427,9 @@
           <t>Sentencia 174: Linaje de Azriel</t>
         </is>
       </c>
+      <c r="K379" t="inlineStr"/>
+      <c r="L379" t="inlineStr"/>
+      <c r="M379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -14313,6 +15462,9 @@
           <t>Sentencia 174: Linaje de Jeremías</t>
         </is>
       </c>
+      <c r="K380" t="inlineStr"/>
+      <c r="L380" t="inlineStr"/>
+      <c r="M380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -14345,6 +15497,9 @@
           <t>Sentencia 174: Linaje de Hodavías</t>
         </is>
       </c>
+      <c r="K381" t="inlineStr"/>
+      <c r="L381" t="inlineStr"/>
+      <c r="M381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -14377,6 +15532,9 @@
           <t>Sentencia 174: Linaje de Jahdiel</t>
         </is>
       </c>
+      <c r="K382" t="inlineStr"/>
+      <c r="L382" t="inlineStr"/>
+      <c r="M382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -14409,6 +15567,9 @@
           <t>Sentencia 174: Linaje de hombres valientes</t>
         </is>
       </c>
+      <c r="K383" t="inlineStr"/>
+      <c r="L383" t="inlineStr"/>
+      <c r="M383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -14443,6 +15604,9 @@
           <t>Sentencia 174: Hijo de esforzados</t>
         </is>
       </c>
+      <c r="K384" t="inlineStr"/>
+      <c r="L384" t="inlineStr"/>
+      <c r="M384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -14477,6 +15641,9 @@
           <t>Sentencia 174: Hijo de esforzados</t>
         </is>
       </c>
+      <c r="K385" t="inlineStr"/>
+      <c r="L385" t="inlineStr"/>
+      <c r="M385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -14511,6 +15678,9 @@
           <t>Sentencia 175: Hijo de Pero se rebelaron contra el Elohim de sus padres</t>
         </is>
       </c>
+      <c r="K386" t="inlineStr"/>
+      <c r="L386" t="inlineStr"/>
+      <c r="M386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -14545,6 +15715,9 @@
           <t>Sentencia 175: Hijo de Pero se rebelaron contra el Elohim de sus padres</t>
         </is>
       </c>
+      <c r="K387" t="inlineStr"/>
+      <c r="L387" t="inlineStr"/>
+      <c r="M387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -14577,6 +15750,9 @@
           <t>Sentencia 176: Linaje de Por lo cual el Elohim de Israel excitó el espíritu de Pul</t>
         </is>
       </c>
+      <c r="K388" t="inlineStr"/>
+      <c r="L388" t="inlineStr"/>
+      <c r="M388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -14609,6 +15785,9 @@
           <t>Sentencia 176: Linaje de rey de Asiria</t>
         </is>
       </c>
+      <c r="K389" t="inlineStr"/>
+      <c r="L389" t="inlineStr"/>
+      <c r="M389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -14641,6 +15820,9 @@
           <t>Sentencia 176: Linaje de espíritu de Tiglat-Pileser</t>
         </is>
       </c>
+      <c r="K390" t="inlineStr"/>
+      <c r="L390" t="inlineStr"/>
+      <c r="M390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -14673,6 +15855,9 @@
           <t>Sentencia 176: Linaje de rey de Asiria</t>
         </is>
       </c>
+      <c r="K391" t="inlineStr"/>
+      <c r="L391" t="inlineStr"/>
+      <c r="M391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -14705,6 +15890,9 @@
           <t>Sentencia 176: Linaje de el cual transportó a los rubenitas</t>
         </is>
       </c>
+      <c r="K392" t="inlineStr"/>
+      <c r="L392" t="inlineStr"/>
+      <c r="M392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -14737,6 +15925,9 @@
           <t>Sentencia 176: Linaje de gaditas</t>
         </is>
       </c>
+      <c r="K393" t="inlineStr"/>
+      <c r="L393" t="inlineStr"/>
+      <c r="M393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -14769,6 +15960,9 @@
           <t>Sentencia 176: Linaje de la media tribu de Manasés</t>
         </is>
       </c>
+      <c r="K394" t="inlineStr"/>
+      <c r="L394" t="inlineStr"/>
+      <c r="M394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -14801,6 +15995,9 @@
           <t>Sentencia 176: Linaje de llevó a Halah</t>
         </is>
       </c>
+      <c r="K395" t="inlineStr"/>
+      <c r="L395" t="inlineStr"/>
+      <c r="M395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -14835,6 +16032,9 @@
           <t>Sentencia 176: Hijo de a Habor</t>
         </is>
       </c>
+      <c r="K396" t="inlineStr"/>
+      <c r="L396" t="inlineStr"/>
+      <c r="M396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -14869,6 +16069,9 @@
           <t>Sentencia 176: Hijo de a Habor</t>
         </is>
       </c>
+      <c r="K397" t="inlineStr"/>
+      <c r="L397" t="inlineStr"/>
+      <c r="M397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -14915,6 +16118,9 @@
           <t>Sentencia 177: Hijos de Leví: Gersón, Coat y Merari</t>
         </is>
       </c>
+      <c r="K398" t="inlineStr"/>
+      <c r="L398" t="inlineStr"/>
+      <c r="M398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -14961,6 +16167,9 @@
           <t>Sentencia 177: Hijos de Leví: Gersón, Coat y Merari</t>
         </is>
       </c>
+      <c r="K399" t="inlineStr"/>
+      <c r="L399" t="inlineStr"/>
+      <c r="M399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -15007,6 +16216,9 @@
           <t>Sentencia 177: Hijos de Leví: Gersón, Coat y Merari</t>
         </is>
       </c>
+      <c r="K400" t="inlineStr"/>
+      <c r="L400" t="inlineStr"/>
+      <c r="M400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -15041,6 +16253,9 @@
           <t>Sentencia 178: Hijos de Coat: Amram, Izhar, Hebrón y Uziel</t>
         </is>
       </c>
+      <c r="K401" t="inlineStr"/>
+      <c r="L401" t="inlineStr"/>
+      <c r="M401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -15075,6 +16290,9 @@
           <t>Sentencia 178: Hijos de Coat: Amram, Izhar, Hebrón y Uziel</t>
         </is>
       </c>
+      <c r="K402" t="inlineStr"/>
+      <c r="L402" t="inlineStr"/>
+      <c r="M402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -15109,6 +16327,9 @@
           <t>Sentencia 178: Hijos de Coat: Amram, Izhar, Hebrón y Uziel</t>
         </is>
       </c>
+      <c r="K403" t="inlineStr"/>
+      <c r="L403" t="inlineStr"/>
+      <c r="M403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -15143,6 +16364,9 @@
           <t>Sentencia 178: Hijos de Coat: Amram, Izhar, Hebrón y Uziel</t>
         </is>
       </c>
+      <c r="K404" t="inlineStr"/>
+      <c r="L404" t="inlineStr"/>
+      <c r="M404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -15185,6 +16409,9 @@
           <t>Sentencia 179: Hijos de Amram: Aarón, Moisés y Miriam</t>
         </is>
       </c>
+      <c r="K405" t="inlineStr"/>
+      <c r="L405" t="inlineStr"/>
+      <c r="M405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -15227,6 +16454,9 @@
           <t>Sentencia 179: Hijos de Amram: Aarón, Moisés y Miriam</t>
         </is>
       </c>
+      <c r="K406" t="inlineStr"/>
+      <c r="L406" t="inlineStr"/>
+      <c r="M406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -15269,6 +16499,9 @@
           <t>Sentencia 179: Hijos de Amram: Aarón, Moisés y Miriam</t>
         </is>
       </c>
+      <c r="K407" t="inlineStr"/>
+      <c r="L407" t="inlineStr"/>
+      <c r="M407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -15315,6 +16548,9 @@
           <t>Sentencia 180: Hijos de Aarón: Nadab, Abiú, Eleazar e Itamar</t>
         </is>
       </c>
+      <c r="K408" t="inlineStr"/>
+      <c r="L408" t="inlineStr"/>
+      <c r="M408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -15361,6 +16597,9 @@
           <t>Sentencia 180: Hijos de Aarón: Nadab, Abiú, Eleazar e Itamar</t>
         </is>
       </c>
+      <c r="K409" t="inlineStr"/>
+      <c r="L409" t="inlineStr"/>
+      <c r="M409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -15407,6 +16646,9 @@
           <t>Sentencia 180: Hijos de Aarón: Nadab, Abiú, Eleazar e Itamar</t>
         </is>
       </c>
+      <c r="K410" t="inlineStr"/>
+      <c r="L410" t="inlineStr"/>
+      <c r="M410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -15453,6 +16695,9 @@
           <t>Sentencia 180: Hijos de Aarón: Nadab, Abiú, Eleazar e Itamar</t>
         </is>
       </c>
+      <c r="K411" t="inlineStr"/>
+      <c r="L411" t="inlineStr"/>
+      <c r="M411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -15485,6 +16730,9 @@
           <t xml:space="preserve">Sentencia 181: Eleazar engendró a Finees, Finees engendró a Abisúa, Abisúa engendró a Buqui, Buqui engendró a Uzi, </t>
         </is>
       </c>
+      <c r="K412" t="inlineStr"/>
+      <c r="L412" t="inlineStr"/>
+      <c r="M412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -15517,6 +16765,9 @@
           <t xml:space="preserve">Sentencia 181: Eleazar engendró a Finees, Finees engendró a Abisúa, Abisúa engendró a Buqui, Buqui engendró a Uzi, </t>
         </is>
       </c>
+      <c r="K413" t="inlineStr"/>
+      <c r="L413" t="inlineStr"/>
+      <c r="M413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -15549,6 +16800,9 @@
           <t xml:space="preserve">Sentencia 181: Eleazar engendró a Finees, Finees engendró a Abisúa, Abisúa engendró a Buqui, Buqui engendró a Uzi, </t>
         </is>
       </c>
+      <c r="K414" t="inlineStr"/>
+      <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -15581,6 +16835,9 @@
           <t xml:space="preserve">Sentencia 181: Eleazar engendró a Finees, Finees engendró a Abisúa, Abisúa engendró a Buqui, Buqui engendró a Uzi, </t>
         </is>
       </c>
+      <c r="K415" t="inlineStr"/>
+      <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -15613,6 +16870,9 @@
           <t xml:space="preserve">Sentencia 181: Eleazar engendró a Finees, Finees engendró a Abisúa, Abisúa engendró a Buqui, Buqui engendró a Uzi, </t>
         </is>
       </c>
+      <c r="K416" t="inlineStr"/>
+      <c r="L416" t="inlineStr"/>
+      <c r="M416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -15645,6 +16905,9 @@
           <t xml:space="preserve">Sentencia 181: Eleazar engendró a Finees, Finees engendró a Abisúa, Abisúa engendró a Buqui, Buqui engendró a Uzi, </t>
         </is>
       </c>
+      <c r="K417" t="inlineStr"/>
+      <c r="L417" t="inlineStr"/>
+      <c r="M417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -15677,6 +16940,9 @@
           <t xml:space="preserve">Sentencia 181: Eleazar engendró a Finees, Finees engendró a Abisúa, Abisúa engendró a Buqui, Buqui engendró a Uzi, </t>
         </is>
       </c>
+      <c r="K418" t="inlineStr"/>
+      <c r="L418" t="inlineStr"/>
+      <c r="M418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -15709,6 +16975,9 @@
           <t xml:space="preserve">Sentencia 181: Eleazar engendró a Finees, Finees engendró a Abisúa, Abisúa engendró a Buqui, Buqui engendró a Uzi, </t>
         </is>
       </c>
+      <c r="K419" t="inlineStr"/>
+      <c r="L419" t="inlineStr"/>
+      <c r="M419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -15741,6 +17010,9 @@
           <t xml:space="preserve">Sentencia 181: Eleazar engendró a Finees, Finees engendró a Abisúa, Abisúa engendró a Buqui, Buqui engendró a Uzi, </t>
         </is>
       </c>
+      <c r="K420" t="inlineStr"/>
+      <c r="L420" t="inlineStr"/>
+      <c r="M420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -15773,6 +17045,9 @@
           <t xml:space="preserve">Sentencia 181: Eleazar engendró a Finees, Finees engendró a Abisúa, Abisúa engendró a Buqui, Buqui engendró a Uzi, </t>
         </is>
       </c>
+      <c r="K421" t="inlineStr"/>
+      <c r="L421" t="inlineStr"/>
+      <c r="M421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -15805,6 +17080,9 @@
           <t xml:space="preserve">Sentencia 181: Eleazar engendró a Finees, Finees engendró a Abisúa, Abisúa engendró a Buqui, Buqui engendró a Uzi, </t>
         </is>
       </c>
+      <c r="K422" t="inlineStr"/>
+      <c r="L422" t="inlineStr"/>
+      <c r="M422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -15837,6 +17115,9 @@
           <t xml:space="preserve">Sentencia 181: Eleazar engendró a Finees, Finees engendró a Abisúa, Abisúa engendró a Buqui, Buqui engendró a Uzi, </t>
         </is>
       </c>
+      <c r="K423" t="inlineStr"/>
+      <c r="L423" t="inlineStr"/>
+      <c r="M423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -15869,6 +17150,9 @@
           <t xml:space="preserve">Sentencia 181: Eleazar engendró a Finees, Finees engendró a Abisúa, Abisúa engendró a Buqui, Buqui engendró a Uzi, </t>
         </is>
       </c>
+      <c r="K424" t="inlineStr"/>
+      <c r="L424" t="inlineStr"/>
+      <c r="M424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -15901,6 +17185,9 @@
           <t>Sentencia 182: Azarías engendró a Amarías, Amarías engendró a Ahitob, Ahitob engendró a Sadoc, Sadoc engendró a Sal</t>
         </is>
       </c>
+      <c r="K425" t="inlineStr"/>
+      <c r="L425" t="inlineStr"/>
+      <c r="M425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -15933,6 +17220,9 @@
           <t>Sentencia 182: Azarías engendró a Amarías, Amarías engendró a Ahitob, Ahitob engendró a Sadoc, Sadoc engendró a Sal</t>
         </is>
       </c>
+      <c r="K426" t="inlineStr"/>
+      <c r="L426" t="inlineStr"/>
+      <c r="M426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -15965,6 +17255,9 @@
           <t>Sentencia 182: Azarías engendró a Amarías, Amarías engendró a Ahitob, Ahitob engendró a Sadoc, Sadoc engendró a Sal</t>
         </is>
       </c>
+      <c r="K427" t="inlineStr"/>
+      <c r="L427" t="inlineStr"/>
+      <c r="M427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -15997,6 +17290,9 @@
           <t>Sentencia 182: Azarías engendró a Amarías, Amarías engendró a Ahitob, Ahitob engendró a Sadoc, Sadoc engendró a Sal</t>
         </is>
       </c>
+      <c r="K428" t="inlineStr"/>
+      <c r="L428" t="inlineStr"/>
+      <c r="M428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -16029,6 +17325,9 @@
           <t>Sentencia 182: Azarías engendró a Amarías, Amarías engendró a Ahitob, Ahitob engendró a Sadoc, Sadoc engendró a Sal</t>
         </is>
       </c>
+      <c r="K429" t="inlineStr"/>
+      <c r="L429" t="inlineStr"/>
+      <c r="M429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -16061,6 +17360,9 @@
           <t>Sentencia 182: Azarías engendró a Amarías, Amarías engendró a Ahitob, Ahitob engendró a Sadoc, Sadoc engendró a Sal</t>
         </is>
       </c>
+      <c r="K430" t="inlineStr"/>
+      <c r="L430" t="inlineStr"/>
+      <c r="M430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -16095,6 +17397,9 @@
           <t>Sentencia 185: Y estos son los nombres de los hijos de Gersón: Libni y Simei</t>
         </is>
       </c>
+      <c r="K431" t="inlineStr"/>
+      <c r="L431" t="inlineStr"/>
+      <c r="M431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -16129,6 +17434,9 @@
           <t>Sentencia 185: Y estos son los nombres de los hijos de Gersón: Libni y Simei</t>
         </is>
       </c>
+      <c r="K432" t="inlineStr"/>
+      <c r="L432" t="inlineStr"/>
+      <c r="M432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -16163,6 +17471,9 @@
           <t>Sentencia 187: Hijos de Merari: Mahli y Musi</t>
         </is>
       </c>
+      <c r="K433" t="inlineStr"/>
+      <c r="L433" t="inlineStr"/>
+      <c r="M433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -16197,6 +17508,9 @@
           <t>Sentencia 187: Hijos de Merari: Mahli y Musi</t>
         </is>
       </c>
+      <c r="K434" t="inlineStr"/>
+      <c r="L434" t="inlineStr"/>
+      <c r="M434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -16231,6 +17545,9 @@
           <t>Sentencia 188: Estas son las familias de Leví según sus descendencias: Gersón: Libni su hijo, Jahat su hijo, Zima s</t>
         </is>
       </c>
+      <c r="K435" t="inlineStr"/>
+      <c r="L435" t="inlineStr"/>
+      <c r="M435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -16265,6 +17582,9 @@
           <t>Sentencia 188: Estas son las familias de Leví según sus descendencias: Gersón: Libni su hijo, Jahat su hijo, Zima s</t>
         </is>
       </c>
+      <c r="K436" t="inlineStr"/>
+      <c r="L436" t="inlineStr"/>
+      <c r="M436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -16299,6 +17619,9 @@
           <t>Sentencia 188: Estas son las familias de Leví según sus descendencias: Gersón: Libni su hijo, Jahat su hijo, Zima s</t>
         </is>
       </c>
+      <c r="K437" t="inlineStr"/>
+      <c r="L437" t="inlineStr"/>
+      <c r="M437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -16333,6 +17656,9 @@
           <t>Sentencia 188: Estas son las familias de Leví según sus descendencias: Gersón: Libni su hijo, Jahat su hijo, Zima s</t>
         </is>
       </c>
+      <c r="K438" t="inlineStr"/>
+      <c r="L438" t="inlineStr"/>
+      <c r="M438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -16367,6 +17693,9 @@
           <t>Sentencia 188: Estas son las familias de Leví según sus descendencias: Gersón: Libni su hijo, Jahat su hijo, Zima s</t>
         </is>
       </c>
+      <c r="K439" t="inlineStr"/>
+      <c r="L439" t="inlineStr"/>
+      <c r="M439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -16401,6 +17730,9 @@
           <t>Sentencia 188: Estas son las familias de Leví según sus descendencias: Gersón: Libni su hijo, Jahat su hijo, Zima s</t>
         </is>
       </c>
+      <c r="K440" t="inlineStr"/>
+      <c r="L440" t="inlineStr"/>
+      <c r="M440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -16435,6 +17767,9 @@
           <t>Sentencia 188: Estas son las familias de Leví según sus descendencias: Gersón: Libni su hijo, Jahat su hijo, Zima s</t>
         </is>
       </c>
+      <c r="K441" t="inlineStr"/>
+      <c r="L441" t="inlineStr"/>
+      <c r="M441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -16469,6 +17804,9 @@
           <t>Sentencia 189: Hijos de Coat: Aminadab su hijo, Coré su hijo, Asir su hijo, Elcana su hijo, Ebiasaf su hijo, Asir s</t>
         </is>
       </c>
+      <c r="K442" t="inlineStr"/>
+      <c r="L442" t="inlineStr"/>
+      <c r="M442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -16503,6 +17841,9 @@
           <t>Sentencia 189: Hijos de Coat: Aminadab su hijo, Coré su hijo, Asir su hijo, Elcana su hijo, Ebiasaf su hijo, Asir s</t>
         </is>
       </c>
+      <c r="K443" t="inlineStr"/>
+      <c r="L443" t="inlineStr"/>
+      <c r="M443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -16537,6 +17878,9 @@
           <t>Sentencia 189: Hijos de Coat: Aminadab su hijo, Coré su hijo, Asir su hijo, Elcana su hijo, Ebiasaf su hijo, Asir s</t>
         </is>
       </c>
+      <c r="K444" t="inlineStr"/>
+      <c r="L444" t="inlineStr"/>
+      <c r="M444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -16571,6 +17915,9 @@
           <t>Sentencia 189: Hijos de Coat: Aminadab su hijo, Coré su hijo, Asir su hijo, Elcana su hijo, Ebiasaf su hijo, Asir s</t>
         </is>
       </c>
+      <c r="K445" t="inlineStr"/>
+      <c r="L445" t="inlineStr"/>
+      <c r="M445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -16605,6 +17952,9 @@
           <t>Sentencia 189: Hijos de Coat: Aminadab su hijo, Coré su hijo, Asir su hijo, Elcana su hijo, Ebiasaf su hijo, Asir s</t>
         </is>
       </c>
+      <c r="K446" t="inlineStr"/>
+      <c r="L446" t="inlineStr"/>
+      <c r="M446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -16639,6 +17989,9 @@
           <t>Sentencia 189: Hijos de Coat: Aminadab su hijo, Coré su hijo, Asir su hijo, Elcana su hijo, Ebiasaf su hijo, Asir s</t>
         </is>
       </c>
+      <c r="K447" t="inlineStr"/>
+      <c r="L447" t="inlineStr"/>
+      <c r="M447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -16673,6 +18026,9 @@
           <t>Sentencia 189: Hijos de Coat: Aminadab su hijo, Coré su hijo, Asir su hijo, Elcana su hijo, Ebiasaf su hijo, Asir s</t>
         </is>
       </c>
+      <c r="K448" t="inlineStr"/>
+      <c r="L448" t="inlineStr"/>
+      <c r="M448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -16707,6 +18063,9 @@
           <t>Sentencia 189: Hijos de Coat: Aminadab su hijo, Coré su hijo, Asir su hijo, Elcana su hijo, Ebiasaf su hijo, Asir s</t>
         </is>
       </c>
+      <c r="K449" t="inlineStr"/>
+      <c r="L449" t="inlineStr"/>
+      <c r="M449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -16741,6 +18100,9 @@
           <t>Sentencia 189: Hijos de Coat: Aminadab su hijo, Coré su hijo, Asir su hijo, Elcana su hijo, Ebiasaf su hijo, Asir s</t>
         </is>
       </c>
+      <c r="K450" t="inlineStr"/>
+      <c r="L450" t="inlineStr"/>
+      <c r="M450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -16775,6 +18137,9 @@
           <t xml:space="preserve">Sentencia 190: Hijos de Elcana: Amasai y Ahimot, padre de Elcana, padre de Zofai, padre  de Nahat, padre de Eliab, </t>
         </is>
       </c>
+      <c r="K451" t="inlineStr"/>
+      <c r="L451" t="inlineStr"/>
+      <c r="M451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -16809,6 +18174,9 @@
           <t xml:space="preserve">Sentencia 190: Hijos de Elcana: Amasai y Ahimot, padre de Elcana, padre de Zofai, padre  de Nahat, padre de Eliab, </t>
         </is>
       </c>
+      <c r="K452" t="inlineStr"/>
+      <c r="L452" t="inlineStr"/>
+      <c r="M452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -16843,6 +18211,9 @@
           <t>Sentencia 191: Hijos de Samuel: Joel  el primogénito, y Abías el segundo</t>
         </is>
       </c>
+      <c r="K453" t="inlineStr"/>
+      <c r="L453" t="inlineStr"/>
+      <c r="M453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -16877,6 +18248,9 @@
           <t>Sentencia 191: Hijos de Samuel: Joel  el primogénito, y Abías el segundo</t>
         </is>
       </c>
+      <c r="K454" t="inlineStr"/>
+      <c r="L454" t="inlineStr"/>
+      <c r="M454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -16911,6 +18285,9 @@
           <t>Sentencia 192: Hijos de Merari: Mahli, Libni su hijo, Simei su hijo, Uza su hijo, Simea su hijo, Haguía su hijo, As</t>
         </is>
       </c>
+      <c r="K455" t="inlineStr"/>
+      <c r="L455" t="inlineStr"/>
+      <c r="M455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -16945,6 +18322,9 @@
           <t>Sentencia 192: Hijos de Merari: Mahli, Libni su hijo, Simei su hijo, Uza su hijo, Simea su hijo, Haguía su hijo, As</t>
         </is>
       </c>
+      <c r="K456" t="inlineStr"/>
+      <c r="L456" t="inlineStr"/>
+      <c r="M456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -16979,6 +18359,9 @@
           <t>Sentencia 192: Hijos de Merari: Mahli, Libni su hijo, Simei su hijo, Uza su hijo, Simea su hijo, Haguía su hijo, As</t>
         </is>
       </c>
+      <c r="K457" t="inlineStr"/>
+      <c r="L457" t="inlineStr"/>
+      <c r="M457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -17013,6 +18396,9 @@
           <t>Sentencia 192: Hijos de Merari: Mahli, Libni su hijo, Simei su hijo, Uza su hijo, Simea su hijo, Haguía su hijo, As</t>
         </is>
       </c>
+      <c r="K458" t="inlineStr"/>
+      <c r="L458" t="inlineStr"/>
+      <c r="M458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -17047,6 +18433,9 @@
           <t>Sentencia 192: Hijos de Merari: Mahli, Libni su hijo, Simei su hijo, Uza su hijo, Simea su hijo, Haguía su hijo, As</t>
         </is>
       </c>
+      <c r="K459" t="inlineStr"/>
+      <c r="L459" t="inlineStr"/>
+      <c r="M459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -17081,6 +18470,9 @@
           <t>Sentencia 192: Hijos de Merari: Mahli, Libni su hijo, Simei su hijo, Uza su hijo, Simea su hijo, Haguía su hijo, As</t>
         </is>
       </c>
+      <c r="K460" t="inlineStr"/>
+      <c r="L460" t="inlineStr"/>
+      <c r="M460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -17113,6 +18505,9 @@
           <t>Sentencia 193: Estos son los que David puso sobre las manos del canto  en la Casa de YHVH desde que el arca había descansado allí es padre de los cuales servían delante de la tienda del tabernáculo de reunión en el canto</t>
         </is>
       </c>
+      <c r="K461" t="inlineStr"/>
+      <c r="L461" t="inlineStr"/>
+      <c r="M461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -17145,6 +18540,9 @@
           <t>Sentencia 193: los cuales servían delante de la tienda del tabernáculo de reunión en el canto es padre de hasta que Salomón edificó la Casa de YHVH en Jerusalén; después estuvieron en su oficio según su costumbre</t>
         </is>
       </c>
+      <c r="K462" t="inlineStr"/>
+      <c r="L462" t="inlineStr"/>
+      <c r="M462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -17179,6 +18577,9 @@
           <t>Sentencia 198: Los hijos de Aarón son estos: Eleazar su hijo, Finees su hijo, Abisúa su hijo, Buqui su hijo, Uzi su</t>
         </is>
       </c>
+      <c r="K463" t="inlineStr"/>
+      <c r="L463" t="inlineStr"/>
+      <c r="M463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -17213,6 +18614,9 @@
           <t>Sentencia 198: Los hijos de Aarón son estos: Eleazar su hijo, Finees su hijo, Abisúa su hijo, Buqui su hijo, Uzi su</t>
         </is>
       </c>
+      <c r="K464" t="inlineStr"/>
+      <c r="L464" t="inlineStr"/>
+      <c r="M464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -17247,6 +18651,9 @@
           <t>Sentencia 198: Los hijos de Aarón son estos: Eleazar su hijo, Finees su hijo, Abisúa su hijo, Buqui su hijo, Uzi su</t>
         </is>
       </c>
+      <c r="K465" t="inlineStr"/>
+      <c r="L465" t="inlineStr"/>
+      <c r="M465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -17281,6 +18688,9 @@
           <t>Sentencia 198: Los hijos de Aarón son estos: Eleazar su hijo, Finees su hijo, Abisúa su hijo, Buqui su hijo, Uzi su</t>
         </is>
       </c>
+      <c r="K466" t="inlineStr"/>
+      <c r="L466" t="inlineStr"/>
+      <c r="M466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -17315,6 +18725,9 @@
           <t>Sentencia 198: Los hijos de Aarón son estos: Eleazar su hijo, Finees su hijo, Abisúa su hijo, Buqui su hijo, Uzi su</t>
         </is>
       </c>
+      <c r="K467" t="inlineStr"/>
+      <c r="L467" t="inlineStr"/>
+      <c r="M467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -17349,6 +18762,9 @@
           <t>Sentencia 198: Los hijos de Aarón son estos: Eleazar su hijo, Finees su hijo, Abisúa su hijo, Buqui su hijo, Uzi su</t>
         </is>
       </c>
+      <c r="K468" t="inlineStr"/>
+      <c r="L468" t="inlineStr"/>
+      <c r="M468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -17383,6 +18799,9 @@
           <t>Sentencia 198: Los hijos de Aarón son estos: Eleazar su hijo, Finees su hijo, Abisúa su hijo, Buqui su hijo, Uzi su</t>
         </is>
       </c>
+      <c r="K469" t="inlineStr"/>
+      <c r="L469" t="inlineStr"/>
+      <c r="M469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -17417,6 +18836,9 @@
           <t>Sentencia 198: Los hijos de Aarón son estos: Eleazar su hijo, Finees su hijo, Abisúa su hijo, Buqui su hijo, Uzi su</t>
         </is>
       </c>
+      <c r="K470" t="inlineStr"/>
+      <c r="L470" t="inlineStr"/>
+      <c r="M470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -17451,6 +18873,9 @@
           <t>Sentencia 198: Los hijos de Aarón son estos: Eleazar su hijo, Finees su hijo, Abisúa su hijo, Buqui su hijo, Uzi su</t>
         </is>
       </c>
+      <c r="K471" t="inlineStr"/>
+      <c r="L471" t="inlineStr"/>
+      <c r="M471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -17485,6 +18910,9 @@
           <t>Sentencia 198: Los hijos de Aarón son estos: Eleazar su hijo, Finees su hijo, Abisúa su hijo, Buqui su hijo, Uzi su</t>
         </is>
       </c>
+      <c r="K472" t="inlineStr"/>
+      <c r="L472" t="inlineStr"/>
+      <c r="M472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -17519,6 +18947,9 @@
           <t>Sentencia 198: Los hijos de Aarón son estos: Eleazar su hijo, Finees su hijo, Abisúa su hijo, Buqui su hijo, Uzi su</t>
         </is>
       </c>
+      <c r="K473" t="inlineStr"/>
+      <c r="L473" t="inlineStr"/>
+      <c r="M473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -17551,6 +18982,9 @@
           <t>Sentencia 200: Linaje de Les dieron pues</t>
         </is>
       </c>
+      <c r="K474" t="inlineStr"/>
+      <c r="L474" t="inlineStr"/>
+      <c r="M474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -17585,6 +19019,9 @@
           <t>Sentencia 200: Hijo de Hebrón</t>
         </is>
       </c>
+      <c r="K475" t="inlineStr"/>
+      <c r="L475" t="inlineStr"/>
+      <c r="M475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -17619,6 +19056,9 @@
           <t>Sentencia 200: Hijo de Hebrón</t>
         </is>
       </c>
+      <c r="K476" t="inlineStr"/>
+      <c r="L476" t="inlineStr"/>
+      <c r="M476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -17653,6 +19093,9 @@
           <t>Sentencia 201: Hijo de Pero el territorio de la ciudad</t>
         </is>
       </c>
+      <c r="K477" t="inlineStr"/>
+      <c r="L477" t="inlineStr"/>
+      <c r="M477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -17687,6 +19130,9 @@
           <t>Sentencia 203: Hijo de de la tribu de Benjamín: Geba con sus ejidos</t>
         </is>
       </c>
+      <c r="K478" t="inlineStr"/>
+      <c r="L478" t="inlineStr"/>
+      <c r="M478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -17721,6 +19167,9 @@
           <t>Sentencia 203: Hijo de de la tribu de Benjamín: Geba con sus ejidos</t>
         </is>
       </c>
+      <c r="K479" t="inlineStr"/>
+      <c r="L479" t="inlineStr"/>
+      <c r="M479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -17753,6 +19202,9 @@
           <t>Sentencia 213: Linaje de la tribu de Isacar: Cedes con sus ejidos</t>
         </is>
       </c>
+      <c r="K480" t="inlineStr"/>
+      <c r="L480" t="inlineStr"/>
+      <c r="M480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -17787,6 +19239,9 @@
           <t>Sentencia 213: Hijo de Daberat con sus ejidos</t>
         </is>
       </c>
+      <c r="K481" t="inlineStr"/>
+      <c r="L481" t="inlineStr"/>
+      <c r="M481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -17821,6 +19276,9 @@
           <t>Sentencia 213: Hijo de Daberat con sus ejidos</t>
         </is>
       </c>
+      <c r="K482" t="inlineStr"/>
+      <c r="L482" t="inlineStr"/>
+      <c r="M482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -17853,6 +19311,9 @@
           <t>Sentencia 214: Linaje de la tribu de Aser: Masal con sus ejidos</t>
         </is>
       </c>
+      <c r="K483" t="inlineStr"/>
+      <c r="L483" t="inlineStr"/>
+      <c r="M483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -17887,6 +19348,9 @@
           <t>Sentencia 214: Hijo de Abdón con sus ejidos</t>
         </is>
       </c>
+      <c r="K484" t="inlineStr"/>
+      <c r="L484" t="inlineStr"/>
+      <c r="M484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -17921,6 +19385,9 @@
           <t>Sentencia 214: Hijo de Abdón con sus ejidos</t>
         </is>
       </c>
+      <c r="K485" t="inlineStr"/>
+      <c r="L485" t="inlineStr"/>
+      <c r="M485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -17953,6 +19420,9 @@
           <t>Sentencia 215: Linaje de la tribu de Neftalí: Cedes</t>
         </is>
       </c>
+      <c r="K486" t="inlineStr"/>
+      <c r="L486" t="inlineStr"/>
+      <c r="M486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -17985,6 +19455,9 @@
           <t>Sentencia 215: Linaje de en Galilea</t>
         </is>
       </c>
+      <c r="K487" t="inlineStr"/>
+      <c r="L487" t="inlineStr"/>
+      <c r="M487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -18019,6 +19492,9 @@
           <t>Sentencia 215: Hijo de con sus ejidos</t>
         </is>
       </c>
+      <c r="K488" t="inlineStr"/>
+      <c r="L488" t="inlineStr"/>
+      <c r="M488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -18053,6 +19529,9 @@
           <t>Sentencia 215: Hijo de con sus ejidos</t>
         </is>
       </c>
+      <c r="K489" t="inlineStr"/>
+      <c r="L489" t="inlineStr"/>
+      <c r="M489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -18085,6 +19564,9 @@
           <t>Sentencia 217: Linaje de Allende el Jordán</t>
         </is>
       </c>
+      <c r="K490" t="inlineStr"/>
+      <c r="L490" t="inlineStr"/>
+      <c r="M490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -18117,6 +19599,9 @@
           <t>Sentencia 217: Linaje de frente a Jericó</t>
         </is>
       </c>
+      <c r="K491" t="inlineStr"/>
+      <c r="L491" t="inlineStr"/>
+      <c r="M491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -18149,6 +19634,9 @@
           <t>Sentencia 217: Linaje de al oriente del Jordán</t>
         </is>
       </c>
+      <c r="K492" t="inlineStr"/>
+      <c r="L492" t="inlineStr"/>
+      <c r="M492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -18181,6 +19669,9 @@
           <t>Sentencia 217: Linaje de de la tribu de Rubén</t>
         </is>
       </c>
+      <c r="K493" t="inlineStr"/>
+      <c r="L493" t="inlineStr"/>
+      <c r="M493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -18213,6 +19704,9 @@
           <t>Sentencia 217: Linaje de dieron Beser</t>
         </is>
       </c>
+      <c r="K494" t="inlineStr"/>
+      <c r="L494" t="inlineStr"/>
+      <c r="M494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -18245,6 +19739,9 @@
           <t>Sentencia 217: Linaje de en el desierto</t>
         </is>
       </c>
+      <c r="K495" t="inlineStr"/>
+      <c r="L495" t="inlineStr"/>
+      <c r="M495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -18277,6 +19774,9 @@
           <t>Sentencia 217: Linaje de con sus ejidos</t>
         </is>
       </c>
+      <c r="K496" t="inlineStr"/>
+      <c r="L496" t="inlineStr"/>
+      <c r="M496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -18311,6 +19811,9 @@
           <t>Sentencia 217: Hijo de Jaza con sus ejidos</t>
         </is>
       </c>
+      <c r="K497" t="inlineStr"/>
+      <c r="L497" t="inlineStr"/>
+      <c r="M497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -18345,6 +19848,9 @@
           <t>Sentencia 217: Hijo de Jaza con sus ejidos</t>
         </is>
       </c>
+      <c r="K498" t="inlineStr"/>
+      <c r="L498" t="inlineStr"/>
+      <c r="M498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -18377,6 +19883,9 @@
           <t>Sentencia 218: Linaje de de la tribu de Gad: Ramot de Galaad con sus ejidos</t>
         </is>
       </c>
+      <c r="K499" t="inlineStr"/>
+      <c r="L499" t="inlineStr"/>
+      <c r="M499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -18411,6 +19920,9 @@
           <t>Sentencia 218: Hijo de Mahanaim con sus ejidos</t>
         </is>
       </c>
+      <c r="K500" t="inlineStr"/>
+      <c r="L500" t="inlineStr"/>
+      <c r="M500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -18445,6 +19957,9 @@
           <t>Sentencia 218: Hijo de Mahanaim con sus ejidos</t>
         </is>
       </c>
+      <c r="K501" t="inlineStr"/>
+      <c r="L501" t="inlineStr"/>
+      <c r="M501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -18479,6 +19994,9 @@
           <t>Sentencia 219: Hijos de Isacar: Tola, Fúa, Jasub y Simrón: cuatro</t>
         </is>
       </c>
+      <c r="K502" t="inlineStr"/>
+      <c r="L502" t="inlineStr"/>
+      <c r="M502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -18513,6 +20031,9 @@
           <t>Sentencia 219: Hijos de Isacar: Tola, Fúa, Jasub y Simrón: cuatro</t>
         </is>
       </c>
+      <c r="K503" t="inlineStr"/>
+      <c r="L503" t="inlineStr"/>
+      <c r="M503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -18547,6 +20068,9 @@
           <t>Sentencia 219: Hijos de Isacar: Tola, Fúa, Jasub y Simrón: cuatro</t>
         </is>
       </c>
+      <c r="K504" t="inlineStr"/>
+      <c r="L504" t="inlineStr"/>
+      <c r="M504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -18581,6 +20105,9 @@
           <t>Sentencia 219: Hijos de Isacar: Tola, Fúa, Jasub y Simrón: cuatro</t>
         </is>
       </c>
+      <c r="K505" t="inlineStr"/>
+      <c r="L505" t="inlineStr"/>
+      <c r="M505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -18615,6 +20142,9 @@
           <t>Sentencia 220: Hijos de Tola: Uzi, Refaías, Jeriel, Jahmai, Jibsam y Semuel, jefes de las familias de sus padres</t>
         </is>
       </c>
+      <c r="K506" t="inlineStr"/>
+      <c r="L506" t="inlineStr"/>
+      <c r="M506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -18649,6 +20179,9 @@
           <t>Sentencia 220: Hijos de Tola: Uzi, Refaías, Jeriel, Jahmai, Jibsam y Semuel, jefes de las familias de sus padres</t>
         </is>
       </c>
+      <c r="K507" t="inlineStr"/>
+      <c r="L507" t="inlineStr"/>
+      <c r="M507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -18683,6 +20216,9 @@
           <t>Sentencia 220: Hijos de Tola: Uzi, Refaías, Jeriel, Jahmai, Jibsam y Semuel, jefes de las familias de sus padres</t>
         </is>
       </c>
+      <c r="K508" t="inlineStr"/>
+      <c r="L508" t="inlineStr"/>
+      <c r="M508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -18717,6 +20253,9 @@
           <t>Sentencia 220: Hijos de Tola: Uzi, Refaías, Jeriel, Jahmai, Jibsam y Semuel, jefes de las familias de sus padres</t>
         </is>
       </c>
+      <c r="K509" t="inlineStr"/>
+      <c r="L509" t="inlineStr"/>
+      <c r="M509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -18751,6 +20290,9 @@
           <t>Sentencia 220: Hijos de Tola: Uzi, Refaías, Jeriel, Jahmai, Jibsam y Semuel, jefes de las familias de sus padres</t>
         </is>
       </c>
+      <c r="K510" t="inlineStr"/>
+      <c r="L510" t="inlineStr"/>
+      <c r="M510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -18785,6 +20327,9 @@
           <t>Sentencia 220: Hijos de Tola: Uzi, Refaías, Jeriel, Jahmai, Jibsam y Semuel, jefes de las familias de sus padres</t>
         </is>
       </c>
+      <c r="K511" t="inlineStr"/>
+      <c r="L511" t="inlineStr"/>
+      <c r="M511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -18819,6 +20364,9 @@
           <t>Sentencia 220: Hijos de Tola: Uzi, Refaías, Jeriel, Jahmai, Jibsam y Semuel, jefes de las familias de sus padres</t>
         </is>
       </c>
+      <c r="K512" t="inlineStr"/>
+      <c r="L512" t="inlineStr"/>
+      <c r="M512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -18853,6 +20401,9 @@
           <t>Sentencia 222: Hijo de Uzi fue Israhías; y los hijos de Israhías: Micael, Obadías, Joel e Isías; por todos, cinco p</t>
         </is>
       </c>
+      <c r="K513" t="inlineStr"/>
+      <c r="L513" t="inlineStr"/>
+      <c r="M513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -18887,6 +20438,9 @@
           <t>Sentencia 222: Hijo de Uzi fue Israhías; y los hijos de Israhías: Micael, Obadías, Joel e Isías; por todos, cinco p</t>
         </is>
       </c>
+      <c r="K514" t="inlineStr"/>
+      <c r="L514" t="inlineStr"/>
+      <c r="M514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -18921,6 +20475,9 @@
           <t>Sentencia 222: Hijo de Uzi fue Israhías; y los hijos de Israhías: Micael, Obadías, Joel e Isías; por todos, cinco p</t>
         </is>
       </c>
+      <c r="K515" t="inlineStr"/>
+      <c r="L515" t="inlineStr"/>
+      <c r="M515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -18955,6 +20512,9 @@
           <t>Sentencia 222: Hijo de Uzi fue Israhías; y los hijos de Israhías: Micael, Obadías, Joel e Isías; por todos, cinco p</t>
         </is>
       </c>
+      <c r="K516" t="inlineStr"/>
+      <c r="L516" t="inlineStr"/>
+      <c r="M516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -18989,6 +20549,9 @@
           <t>Sentencia 222: Hijo de Uzi fue Israhías; y los hijos de Israhías: Micael, Obadías, Joel e Isías; por todos, cinco p</t>
         </is>
       </c>
+      <c r="K517" t="inlineStr"/>
+      <c r="L517" t="inlineStr"/>
+      <c r="M517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -19021,6 +20584,9 @@
           <t>Sentencia 224: Linaje de sus hermanos por todas las familias de Isacar</t>
         </is>
       </c>
+      <c r="K518" t="inlineStr"/>
+      <c r="L518" t="inlineStr"/>
+      <c r="M518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -19055,6 +20621,9 @@
           <t>Sentencia 224: Hijo de contados todos por sus genealogías</t>
         </is>
       </c>
+      <c r="K519" t="inlineStr"/>
+      <c r="L519" t="inlineStr"/>
+      <c r="M519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -19089,6 +20658,9 @@
           <t>Sentencia 224: Hijo de contados todos por sus genealogías</t>
         </is>
       </c>
+      <c r="K520" t="inlineStr"/>
+      <c r="L520" t="inlineStr"/>
+      <c r="M520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -19135,6 +20707,9 @@
           <t>Sentencia 225: Hijos de Benjamín: Bela, Bequer y Jediael: tres</t>
         </is>
       </c>
+      <c r="K521" t="inlineStr"/>
+      <c r="L521" t="inlineStr"/>
+      <c r="M521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -19181,6 +20756,9 @@
           <t>Sentencia 225: Hijos de Benjamín: Bela, Bequer y Jediael: tres</t>
         </is>
       </c>
+      <c r="K522" t="inlineStr"/>
+      <c r="L522" t="inlineStr"/>
+      <c r="M522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -19227,6 +20805,9 @@
           <t>Sentencia 225: Hijos de Benjamín: Bela, Bequer y Jediael: tres</t>
         </is>
       </c>
+      <c r="K523" t="inlineStr"/>
+      <c r="L523" t="inlineStr"/>
+      <c r="M523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -19261,6 +20842,9 @@
           <t xml:space="preserve">Sentencia 226: Hijos de Bela: Ezbón, Uzi, Uziel, Jerimot e Iri: cinco jefes de casas paternas, hombres de valor, y </t>
         </is>
       </c>
+      <c r="K524" t="inlineStr"/>
+      <c r="L524" t="inlineStr"/>
+      <c r="M524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -19295,6 +20879,9 @@
           <t xml:space="preserve">Sentencia 226: Hijos de Bela: Ezbón, Uzi, Uziel, Jerimot e Iri: cinco jefes de casas paternas, hombres de valor, y </t>
         </is>
       </c>
+      <c r="K525" t="inlineStr"/>
+      <c r="L525" t="inlineStr"/>
+      <c r="M525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -19329,6 +20916,9 @@
           <t xml:space="preserve">Sentencia 226: Hijos de Bela: Ezbón, Uzi, Uziel, Jerimot e Iri: cinco jefes de casas paternas, hombres de valor, y </t>
         </is>
       </c>
+      <c r="K526" t="inlineStr"/>
+      <c r="L526" t="inlineStr"/>
+      <c r="M526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -19363,6 +20953,9 @@
           <t xml:space="preserve">Sentencia 226: Hijos de Bela: Ezbón, Uzi, Uziel, Jerimot e Iri: cinco jefes de casas paternas, hombres de valor, y </t>
         </is>
       </c>
+      <c r="K527" t="inlineStr"/>
+      <c r="L527" t="inlineStr"/>
+      <c r="M527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -19397,6 +20990,9 @@
           <t xml:space="preserve">Sentencia 226: Hijos de Bela: Ezbón, Uzi, Uziel, Jerimot e Iri: cinco jefes de casas paternas, hombres de valor, y </t>
         </is>
       </c>
+      <c r="K528" t="inlineStr"/>
+      <c r="L528" t="inlineStr"/>
+      <c r="M528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -19431,6 +21027,9 @@
           <t xml:space="preserve">Sentencia 226: Hijos de Bela: Ezbón, Uzi, Uziel, Jerimot e Iri: cinco jefes de casas paternas, hombres de valor, y </t>
         </is>
       </c>
+      <c r="K529" t="inlineStr"/>
+      <c r="L529" t="inlineStr"/>
+      <c r="M529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -19465,6 +21064,9 @@
           <t xml:space="preserve">Sentencia 226: Hijos de Bela: Ezbón, Uzi, Uziel, Jerimot e Iri: cinco jefes de casas paternas, hombres de valor, y </t>
         </is>
       </c>
+      <c r="K530" t="inlineStr"/>
+      <c r="L530" t="inlineStr"/>
+      <c r="M530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -19499,6 +21101,9 @@
           <t xml:space="preserve">Sentencia 226: Hijos de Bela: Ezbón, Uzi, Uziel, Jerimot e Iri: cinco jefes de casas paternas, hombres de valor, y </t>
         </is>
       </c>
+      <c r="K531" t="inlineStr"/>
+      <c r="L531" t="inlineStr"/>
+      <c r="M531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -19533,6 +21138,9 @@
           <t>Sentencia 227: Hijos de Bequer: Zemira, Joás, Eliezer, Elioenai, Omri, Jerimot, Abías, Anatot y Alamet; todos estos</t>
         </is>
       </c>
+      <c r="K532" t="inlineStr"/>
+      <c r="L532" t="inlineStr"/>
+      <c r="M532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -19567,6 +21175,9 @@
           <t>Sentencia 227: Hijos de Bequer: Zemira, Joás, Eliezer, Elioenai, Omri, Jerimot, Abías, Anatot y Alamet; todos estos</t>
         </is>
       </c>
+      <c r="K533" t="inlineStr"/>
+      <c r="L533" t="inlineStr"/>
+      <c r="M533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -19601,6 +21212,9 @@
           <t>Sentencia 227: Hijos de Bequer: Zemira, Joás, Eliezer, Elioenai, Omri, Jerimot, Abías, Anatot y Alamet; todos estos</t>
         </is>
       </c>
+      <c r="K534" t="inlineStr"/>
+      <c r="L534" t="inlineStr"/>
+      <c r="M534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -19635,6 +21249,9 @@
           <t>Sentencia 227: Hijos de Bequer: Zemira, Joás, Eliezer, Elioenai, Omri, Jerimot, Abías, Anatot y Alamet; todos estos</t>
         </is>
       </c>
+      <c r="K535" t="inlineStr"/>
+      <c r="L535" t="inlineStr"/>
+      <c r="M535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -19669,6 +21286,9 @@
           <t>Sentencia 227: Hijos de Bequer: Zemira, Joás, Eliezer, Elioenai, Omri, Jerimot, Abías, Anatot y Alamet; todos estos</t>
         </is>
       </c>
+      <c r="K536" t="inlineStr"/>
+      <c r="L536" t="inlineStr"/>
+      <c r="M536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -19703,6 +21323,9 @@
           <t>Sentencia 227: Hijos de Bequer: Zemira, Joás, Eliezer, Elioenai, Omri, Jerimot, Abías, Anatot y Alamet; todos estos</t>
         </is>
       </c>
+      <c r="K537" t="inlineStr"/>
+      <c r="L537" t="inlineStr"/>
+      <c r="M537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -19737,6 +21360,9 @@
           <t>Sentencia 227: Hijos de Bequer: Zemira, Joás, Eliezer, Elioenai, Omri, Jerimot, Abías, Anatot y Alamet; todos estos</t>
         </is>
       </c>
+      <c r="K538" t="inlineStr"/>
+      <c r="L538" t="inlineStr"/>
+      <c r="M538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -19771,6 +21397,9 @@
           <t>Sentencia 227: Hijos de Bequer: Zemira, Joás, Eliezer, Elioenai, Omri, Jerimot, Abías, Anatot y Alamet; todos estos</t>
         </is>
       </c>
+      <c r="K539" t="inlineStr"/>
+      <c r="L539" t="inlineStr"/>
+      <c r="M539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -19805,6 +21434,9 @@
           <t>Sentencia 227: Hijos de Bequer: Zemira, Joás, Eliezer, Elioenai, Omri, Jerimot, Abías, Anatot y Alamet; todos estos</t>
         </is>
       </c>
+      <c r="K540" t="inlineStr"/>
+      <c r="L540" t="inlineStr"/>
+      <c r="M540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -19839,6 +21471,9 @@
           <t>Sentencia 228: Hijo de contados por sus descendencias</t>
         </is>
       </c>
+      <c r="K541" t="inlineStr"/>
+      <c r="L541" t="inlineStr"/>
+      <c r="M541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -19873,6 +21508,9 @@
           <t>Sentencia 228: Hijo de contados por sus descendencias</t>
         </is>
       </c>
+      <c r="K542" t="inlineStr"/>
+      <c r="L542" t="inlineStr"/>
+      <c r="M542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -19907,6 +21545,9 @@
           <t>Sentencia 229: Hijo de Jediael fue Bilhán; y los hijos de Bilhán: Jeús, Benjamín, Aod, Quenaana, Zetán, Tarsis y Ah</t>
         </is>
       </c>
+      <c r="K543" t="inlineStr"/>
+      <c r="L543" t="inlineStr"/>
+      <c r="M543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -19949,6 +21590,9 @@
           <t>Sentencia 229: Hijo de Jediael fue Bilhán; y los hijos de Bilhán: Jeús, Benjamín, Aod, Quenaana, Zetán, Tarsis y Ah</t>
         </is>
       </c>
+      <c r="K544" t="inlineStr"/>
+      <c r="L544" t="inlineStr"/>
+      <c r="M544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -19983,6 +21627,9 @@
           <t>Sentencia 229: Hijo de Jediael fue Bilhán; y los hijos de Bilhán: Jeús, Benjamín, Aod, Quenaana, Zetán, Tarsis y Ah</t>
         </is>
       </c>
+      <c r="K545" t="inlineStr"/>
+      <c r="L545" t="inlineStr"/>
+      <c r="M545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -20017,6 +21664,9 @@
           <t>Sentencia 229: Hijo de Jediael fue Bilhán; y los hijos de Bilhán: Jeús, Benjamín, Aod, Quenaana, Zetán, Tarsis y Ah</t>
         </is>
       </c>
+      <c r="K546" t="inlineStr"/>
+      <c r="L546" t="inlineStr"/>
+      <c r="M546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -20051,6 +21701,9 @@
           <t>Sentencia 229: Hijo de Jediael fue Bilhán; y los hijos de Bilhán: Jeús, Benjamín, Aod, Quenaana, Zetán, Tarsis y Ah</t>
         </is>
       </c>
+      <c r="K547" t="inlineStr"/>
+      <c r="L547" t="inlineStr"/>
+      <c r="M547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -20085,6 +21738,9 @@
           <t>Sentencia 229: Hijo de Jediael fue Bilhán; y los hijos de Bilhán: Jeús, Benjamín, Aod, Quenaana, Zetán, Tarsis y Ah</t>
         </is>
       </c>
+      <c r="K548" t="inlineStr"/>
+      <c r="L548" t="inlineStr"/>
+      <c r="M548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -20119,6 +21775,9 @@
           <t>Sentencia 229: Hijo de Jediael fue Bilhán; y los hijos de Bilhán: Jeús, Benjamín, Aod, Quenaana, Zetán, Tarsis y Ah</t>
         </is>
       </c>
+      <c r="K549" t="inlineStr"/>
+      <c r="L549" t="inlineStr"/>
+      <c r="M549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -20153,6 +21812,9 @@
           <t>Sentencia 232: Hijos de Neftalí: Jahzeel, Guni, Jezer y Salum, hijos de Bilha</t>
         </is>
       </c>
+      <c r="K550" t="inlineStr"/>
+      <c r="L550" t="inlineStr"/>
+      <c r="M550" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -20187,6 +21849,9 @@
           <t>Sentencia 232: Hijos de Neftalí: Jahzeel, Guni, Jezer y Salum, hijos de Bilha</t>
         </is>
       </c>
+      <c r="K551" t="inlineStr"/>
+      <c r="L551" t="inlineStr"/>
+      <c r="M551" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -20221,6 +21886,9 @@
           <t>Sentencia 232: Hijos de Neftalí: Jahzeel, Guni, Jezer y Salum, hijos de Bilha</t>
         </is>
       </c>
+      <c r="K552" t="inlineStr"/>
+      <c r="L552" t="inlineStr"/>
+      <c r="M552" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -20255,6 +21923,9 @@
           <t>Sentencia 232: Hijos de Neftalí: Jahzeel, Guni, Jezer y Salum, hijos de Bilha</t>
         </is>
       </c>
+      <c r="K553" t="inlineStr"/>
+      <c r="L553" t="inlineStr"/>
+      <c r="M553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -20289,6 +21960,9 @@
           <t>Sentencia 233: Hijos de Manasés: Asriel, al cual dio a luz su concubina la siria, la cual también dio a luz a Maqui</t>
         </is>
       </c>
+      <c r="K554" t="inlineStr"/>
+      <c r="L554" t="inlineStr"/>
+      <c r="M554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -20323,6 +21997,9 @@
           <t>Sentencia 233: Hijos de Manasés: Asriel, al cual dio a luz su concubina la siria, la cual también dio a luz a Maqui</t>
         </is>
       </c>
+      <c r="K555" t="inlineStr"/>
+      <c r="L555" t="inlineStr"/>
+      <c r="M555" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -20357,6 +22034,9 @@
           <t>Sentencia 233: Hijos de Manasés: Asriel, al cual dio a luz su concubina la siria, la cual también dio a luz a Maqui</t>
         </is>
       </c>
+      <c r="K556" t="inlineStr"/>
+      <c r="L556" t="inlineStr"/>
+      <c r="M556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -20395,6 +22075,9 @@
           <t>Sentencia 239: Y su hermana Hamolequet dio a luz a Isod, Abiezer, Mahala y Semida, hijos del cual fueron Ahián, Siq</t>
         </is>
       </c>
+      <c r="K557" t="inlineStr"/>
+      <c r="L557" t="inlineStr"/>
+      <c r="M557" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -20433,6 +22116,9 @@
           <t>Sentencia 239: Y su hermana Hamolequet dio a luz a Isod, Abiezer, Mahala y Semida, hijos del cual fueron Ahián, Siq</t>
         </is>
       </c>
+      <c r="K558" t="inlineStr"/>
+      <c r="L558" t="inlineStr"/>
+      <c r="M558" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -20471,6 +22157,9 @@
           <t>Sentencia 239: Y su hermana Hamolequet dio a luz a Isod, Abiezer, Mahala y Semida, hijos del cual fueron Ahián, Siq</t>
         </is>
       </c>
+      <c r="K559" t="inlineStr"/>
+      <c r="L559" t="inlineStr"/>
+      <c r="M559" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -20509,6 +22198,9 @@
           <t>Sentencia 239: Y su hermana Hamolequet dio a luz a Isod, Abiezer, Mahala y Semida, hijos del cual fueron Ahián, Siq</t>
         </is>
       </c>
+      <c r="K560" t="inlineStr"/>
+      <c r="L560" t="inlineStr"/>
+      <c r="M560" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -20547,6 +22239,9 @@
           <t>Sentencia 239: Y su hermana Hamolequet dio a luz a Isod, Abiezer, Mahala y Semida, hijos del cual fueron Ahián, Siq</t>
         </is>
       </c>
+      <c r="K561" t="inlineStr"/>
+      <c r="L561" t="inlineStr"/>
+      <c r="M561" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -20585,6 +22280,9 @@
           <t>Sentencia 239: Y su hermana Hamolequet dio a luz a Isod, Abiezer, Mahala y Semida, hijos del cual fueron Ahián, Siq</t>
         </is>
       </c>
+      <c r="K562" t="inlineStr"/>
+      <c r="L562" t="inlineStr"/>
+      <c r="M562" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -20623,6 +22321,9 @@
           <t>Sentencia 239: Y su hermana Hamolequet dio a luz a Isod, Abiezer, Mahala y Semida, hijos del cual fueron Ahián, Siq</t>
         </is>
       </c>
+      <c r="K563" t="inlineStr"/>
+      <c r="L563" t="inlineStr"/>
+      <c r="M563" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -20657,6 +22358,9 @@
           <t>Sentencia 240: Los hijos de Efraín: Sutela, Bered su hijo, Tahat su hijo, Elada su hijo, Tahat su hijo, Zabad su hi</t>
         </is>
       </c>
+      <c r="K564" t="inlineStr"/>
+      <c r="L564" t="inlineStr"/>
+      <c r="M564" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -20691,6 +22395,9 @@
           <t>Sentencia 240: Los hijos de Efraín: Sutela, Bered su hijo, Tahat su hijo, Elada su hijo, Tahat su hijo, Zabad su hi</t>
         </is>
       </c>
+      <c r="K565" t="inlineStr"/>
+      <c r="L565" t="inlineStr"/>
+      <c r="M565" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -20725,6 +22432,9 @@
           <t>Sentencia 240: Los hijos de Efraín: Sutela, Bered su hijo, Tahat su hijo, Elada su hijo, Tahat su hijo, Zabad su hi</t>
         </is>
       </c>
+      <c r="K566" t="inlineStr"/>
+      <c r="L566" t="inlineStr"/>
+      <c r="M566" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -20759,6 +22469,9 @@
           <t>Sentencia 240: Los hijos de Efraín: Sutela, Bered su hijo, Tahat su hijo, Elada su hijo, Tahat su hijo, Zabad su hi</t>
         </is>
       </c>
+      <c r="K567" t="inlineStr"/>
+      <c r="L567" t="inlineStr"/>
+      <c r="M567" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -20793,6 +22506,9 @@
           <t>Sentencia 240: Los hijos de Efraín: Sutela, Bered su hijo, Tahat su hijo, Elada su hijo, Tahat su hijo, Zabad su hi</t>
         </is>
       </c>
+      <c r="K568" t="inlineStr"/>
+      <c r="L568" t="inlineStr"/>
+      <c r="M568" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -20827,6 +22543,9 @@
           <t>Sentencia 240: Los hijos de Efraín: Sutela, Bered su hijo, Tahat su hijo, Elada su hijo, Tahat su hijo, Zabad su hi</t>
         </is>
       </c>
+      <c r="K569" t="inlineStr"/>
+      <c r="L569" t="inlineStr"/>
+      <c r="M569" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -20861,6 +22580,9 @@
           <t>Sentencia 240: Los hijos de Efraín: Sutela, Bered su hijo, Tahat su hijo, Elada su hijo, Tahat su hijo, Zabad su hi</t>
         </is>
       </c>
+      <c r="K570" t="inlineStr"/>
+      <c r="L570" t="inlineStr"/>
+      <c r="M570" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -20895,6 +22617,9 @@
           <t>Sentencia 240: Los hijos de Efraín: Sutela, Bered su hijo, Tahat su hijo, Elada su hijo, Tahat su hijo, Zabad su hi</t>
         </is>
       </c>
+      <c r="K571" t="inlineStr"/>
+      <c r="L571" t="inlineStr"/>
+      <c r="M571" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -20927,6 +22652,9 @@
           <t>Sentencia 241: Pero los de Gat es padre de naturales de aquella tierra</t>
         </is>
       </c>
+      <c r="K572" t="inlineStr"/>
+      <c r="L572" t="inlineStr"/>
+      <c r="M572" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -20959,6 +22687,9 @@
           <t>Sentencia 241: naturales de aquella tierra es padre de los mataron porque habían bajado a tomar sus ganados</t>
         </is>
       </c>
+      <c r="K573" t="inlineStr"/>
+      <c r="L573" t="inlineStr"/>
+      <c r="M573" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -20993,6 +22724,9 @@
           <t>Sentencia 248: Hijos de Aser: Imna, Isúa, Isúi, Bería, y su hermana Sera</t>
         </is>
       </c>
+      <c r="K574" t="inlineStr"/>
+      <c r="L574" t="inlineStr"/>
+      <c r="M574" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -21027,6 +22761,9 @@
           <t>Sentencia 248: Hijos de Aser: Imna, Isúa, Isúi, Bería, y su hermana Sera</t>
         </is>
       </c>
+      <c r="K575" t="inlineStr"/>
+      <c r="L575" t="inlineStr"/>
+      <c r="M575" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -21061,6 +22798,9 @@
           <t>Sentencia 248: Hijos de Aser: Imna, Isúa, Isúi, Bería, y su hermana Sera</t>
         </is>
       </c>
+      <c r="K576" t="inlineStr"/>
+      <c r="L576" t="inlineStr"/>
+      <c r="M576" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -21095,6 +22835,9 @@
           <t>Sentencia 248: Hijos de Aser: Imna, Isúa, Isúi, Bería, y su hermana Sera</t>
         </is>
       </c>
+      <c r="K577" t="inlineStr"/>
+      <c r="L577" t="inlineStr"/>
+      <c r="M577" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -21129,6 +22872,9 @@
           <t>Sentencia 248: Hijos de Aser: Imna, Isúa, Isúi, Bería, y su hermana Sera</t>
         </is>
       </c>
+      <c r="K578" t="inlineStr"/>
+      <c r="L578" t="inlineStr"/>
+      <c r="M578" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
@@ -21171,6 +22917,9 @@
           <t>Sentencia 249: Hijos de Bería: Heber, y Malquiel, el cual fue padre de Birzavit</t>
         </is>
       </c>
+      <c r="K579" t="inlineStr"/>
+      <c r="L579" t="inlineStr"/>
+      <c r="M579" t="inlineStr"/>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
@@ -21205,6 +22954,9 @@
           <t>Sentencia 249: Hijos de Bería: Heber, y Malquiel, el cual fue padre de Birzavit</t>
         </is>
       </c>
+      <c r="K580" t="inlineStr"/>
+      <c r="L580" t="inlineStr"/>
+      <c r="M580" t="inlineStr"/>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -21239,6 +22991,9 @@
           <t>Sentencia 249: Hijos de Bería: Heber, y Malquiel, el cual fue padre de Birzavit</t>
         </is>
       </c>
+      <c r="K581" t="inlineStr"/>
+      <c r="L581" t="inlineStr"/>
+      <c r="M581" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
@@ -21283,6 +23038,9 @@
           <t>Sentencia 250: Y Heber engendró a Jaflet, Semer, Hotam, y Súa, hermana de ellos</t>
         </is>
       </c>
+      <c r="K582" t="inlineStr"/>
+      <c r="L582" t="inlineStr"/>
+      <c r="M582" t="inlineStr"/>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -21317,6 +23075,9 @@
           <t>Sentencia 251: Hijos de Jaflet: Pasac, Bimhal y Asvat</t>
         </is>
       </c>
+      <c r="K583" t="inlineStr"/>
+      <c r="L583" t="inlineStr"/>
+      <c r="M583" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
@@ -21351,6 +23112,9 @@
           <t>Sentencia 251: Hijos de Jaflet: Pasac, Bimhal y Asvat</t>
         </is>
       </c>
+      <c r="K584" t="inlineStr"/>
+      <c r="L584" t="inlineStr"/>
+      <c r="M584" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -21385,6 +23149,9 @@
           <t>Sentencia 251: Hijos de Jaflet: Pasac, Bimhal y Asvat</t>
         </is>
       </c>
+      <c r="K585" t="inlineStr"/>
+      <c r="L585" t="inlineStr"/>
+      <c r="M585" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
@@ -21419,6 +23186,9 @@
           <t>Sentencia 253: Hijos de Semer: Ahí, Rohga, Jehúba y Aram</t>
         </is>
       </c>
+      <c r="K586" t="inlineStr"/>
+      <c r="L586" t="inlineStr"/>
+      <c r="M586" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
@@ -21453,6 +23223,9 @@
           <t>Sentencia 253: Hijos de Semer: Ahí, Rohga, Jehúba y Aram</t>
         </is>
       </c>
+      <c r="K587" t="inlineStr"/>
+      <c r="L587" t="inlineStr"/>
+      <c r="M587" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
@@ -21487,6 +23260,9 @@
           <t>Sentencia 253: Hijos de Semer: Ahí, Rohga, Jehúba y Aram</t>
         </is>
       </c>
+      <c r="K588" t="inlineStr"/>
+      <c r="L588" t="inlineStr"/>
+      <c r="M588" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
@@ -21521,6 +23297,9 @@
           <t>Sentencia 253: Hijos de Semer: Ahí, Rohga, Jehúba y Aram</t>
         </is>
       </c>
+      <c r="K589" t="inlineStr"/>
+      <c r="L589" t="inlineStr"/>
+      <c r="M589" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
@@ -21555,6 +23334,9 @@
           <t>Sentencia 254: Hijos de Helem su hermano: Zofa, Imna, Seles y Amal</t>
         </is>
       </c>
+      <c r="K590" t="inlineStr"/>
+      <c r="L590" t="inlineStr"/>
+      <c r="M590" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
@@ -21589,6 +23371,9 @@
           <t>Sentencia 254: Hijos de Helem su hermano: Zofa, Imna, Seles y Amal</t>
         </is>
       </c>
+      <c r="K591" t="inlineStr"/>
+      <c r="L591" t="inlineStr"/>
+      <c r="M591" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
@@ -21623,6 +23408,9 @@
           <t>Sentencia 254: Hijos de Helem su hermano: Zofa, Imna, Seles y Amal</t>
         </is>
       </c>
+      <c r="K592" t="inlineStr"/>
+      <c r="L592" t="inlineStr"/>
+      <c r="M592" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
@@ -21657,6 +23445,9 @@
           <t>Sentencia 254: Hijos de Helem su hermano: Zofa, Imna, Seles y Amal</t>
         </is>
       </c>
+      <c r="K593" t="inlineStr"/>
+      <c r="L593" t="inlineStr"/>
+      <c r="M593" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -21691,6 +23482,9 @@
           <t>Sentencia 255: Hijos de Zofa: Súa, Harnefer, Súal, Beri, Imra, Beser, Hod, Sama, Silsa, Itrán y Beera</t>
         </is>
       </c>
+      <c r="K594" t="inlineStr"/>
+      <c r="L594" t="inlineStr"/>
+      <c r="M594" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -21725,6 +23519,9 @@
           <t>Sentencia 255: Hijos de Zofa: Súa, Harnefer, Súal, Beri, Imra, Beser, Hod, Sama, Silsa, Itrán y Beera</t>
         </is>
       </c>
+      <c r="K595" t="inlineStr"/>
+      <c r="L595" t="inlineStr"/>
+      <c r="M595" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
@@ -21759,6 +23556,9 @@
           <t>Sentencia 255: Hijos de Zofa: Súa, Harnefer, Súal, Beri, Imra, Beser, Hod, Sama, Silsa, Itrán y Beera</t>
         </is>
       </c>
+      <c r="K596" t="inlineStr"/>
+      <c r="L596" t="inlineStr"/>
+      <c r="M596" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
@@ -21793,6 +23593,9 @@
           <t>Sentencia 255: Hijos de Zofa: Súa, Harnefer, Súal, Beri, Imra, Beser, Hod, Sama, Silsa, Itrán y Beera</t>
         </is>
       </c>
+      <c r="K597" t="inlineStr"/>
+      <c r="L597" t="inlineStr"/>
+      <c r="M597" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
@@ -21827,6 +23630,9 @@
           <t>Sentencia 255: Hijos de Zofa: Súa, Harnefer, Súal, Beri, Imra, Beser, Hod, Sama, Silsa, Itrán y Beera</t>
         </is>
       </c>
+      <c r="K598" t="inlineStr"/>
+      <c r="L598" t="inlineStr"/>
+      <c r="M598" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
@@ -21861,6 +23667,9 @@
           <t>Sentencia 255: Hijos de Zofa: Súa, Harnefer, Súal, Beri, Imra, Beser, Hod, Sama, Silsa, Itrán y Beera</t>
         </is>
       </c>
+      <c r="K599" t="inlineStr"/>
+      <c r="L599" t="inlineStr"/>
+      <c r="M599" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
@@ -21895,6 +23704,9 @@
           <t>Sentencia 255: Hijos de Zofa: Súa, Harnefer, Súal, Beri, Imra, Beser, Hod, Sama, Silsa, Itrán y Beera</t>
         </is>
       </c>
+      <c r="K600" t="inlineStr"/>
+      <c r="L600" t="inlineStr"/>
+      <c r="M600" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
@@ -21929,6 +23741,9 @@
           <t>Sentencia 255: Hijos de Zofa: Súa, Harnefer, Súal, Beri, Imra, Beser, Hod, Sama, Silsa, Itrán y Beera</t>
         </is>
       </c>
+      <c r="K601" t="inlineStr"/>
+      <c r="L601" t="inlineStr"/>
+      <c r="M601" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
@@ -21963,6 +23778,9 @@
           <t>Sentencia 255: Hijos de Zofa: Súa, Harnefer, Súal, Beri, Imra, Beser, Hod, Sama, Silsa, Itrán y Beera</t>
         </is>
       </c>
+      <c r="K602" t="inlineStr"/>
+      <c r="L602" t="inlineStr"/>
+      <c r="M602" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
@@ -21997,6 +23815,9 @@
           <t>Sentencia 255: Hijos de Zofa: Súa, Harnefer, Súal, Beri, Imra, Beser, Hod, Sama, Silsa, Itrán y Beera</t>
         </is>
       </c>
+      <c r="K603" t="inlineStr"/>
+      <c r="L603" t="inlineStr"/>
+      <c r="M603" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
@@ -22031,6 +23852,9 @@
           <t>Sentencia 255: Hijos de Zofa: Súa, Harnefer, Súal, Beri, Imra, Beser, Hod, Sama, Silsa, Itrán y Beera</t>
         </is>
       </c>
+      <c r="K604" t="inlineStr"/>
+      <c r="L604" t="inlineStr"/>
+      <c r="M604" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
@@ -22065,6 +23889,9 @@
           <t>Sentencia 256: Hijos de Jeter: Jefone, Pispa y Ara</t>
         </is>
       </c>
+      <c r="K605" t="inlineStr"/>
+      <c r="L605" t="inlineStr"/>
+      <c r="M605" t="inlineStr"/>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
@@ -22099,6 +23926,9 @@
           <t>Sentencia 256: Hijos de Jeter: Jefone, Pispa y Ara</t>
         </is>
       </c>
+      <c r="K606" t="inlineStr"/>
+      <c r="L606" t="inlineStr"/>
+      <c r="M606" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
@@ -22133,6 +23963,9 @@
           <t>Sentencia 256: Hijos de Jeter: Jefone, Pispa y Ara</t>
         </is>
       </c>
+      <c r="K607" t="inlineStr"/>
+      <c r="L607" t="inlineStr"/>
+      <c r="M607" t="inlineStr"/>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
@@ -22167,6 +24000,9 @@
           <t>Sentencia 257: Hijos de Ula: Ara, Haniel y Rezia</t>
         </is>
       </c>
+      <c r="K608" t="inlineStr"/>
+      <c r="L608" t="inlineStr"/>
+      <c r="M608" t="inlineStr"/>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
@@ -22201,6 +24037,9 @@
           <t>Sentencia 257: Hijos de Ula: Ara, Haniel y Rezia</t>
         </is>
       </c>
+      <c r="K609" t="inlineStr"/>
+      <c r="L609" t="inlineStr"/>
+      <c r="M609" t="inlineStr"/>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
@@ -22235,6 +24074,9 @@
           <t>Sentencia 257: Hijos de Ula: Ara, Haniel y Rezia</t>
         </is>
       </c>
+      <c r="K610" t="inlineStr"/>
+      <c r="L610" t="inlineStr"/>
+      <c r="M610" t="inlineStr"/>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
@@ -22281,6 +24123,9 @@
           <t xml:space="preserve">Sentencia 259: Benjamín engendró a Bela su primogénito, Asbel el segundo, Ahara el tercero, Noha el cuarto, y Rafa </t>
         </is>
       </c>
+      <c r="K611" t="inlineStr"/>
+      <c r="L611" t="inlineStr"/>
+      <c r="M611" t="inlineStr"/>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
@@ -22313,6 +24158,9 @@
           <t>Sentencia 264: Y de Husim engendró a Abitob y a Elpaal</t>
         </is>
       </c>
+      <c r="K612" t="inlineStr"/>
+      <c r="L612" t="inlineStr"/>
+      <c r="M612" t="inlineStr"/>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
@@ -22355,6 +24203,9 @@
           <t>Sentencia 265: Hijos de Elpaal: Heber, Misam y Semed, el cual edificó Ono, y Lod con sus aldeas</t>
         </is>
       </c>
+      <c r="K613" t="inlineStr"/>
+      <c r="L613" t="inlineStr"/>
+      <c r="M613" t="inlineStr"/>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
@@ -22389,6 +24240,9 @@
           <t>Sentencia 265: Hijos de Elpaal: Heber, Misam y Semed, el cual edificó Ono, y Lod con sus aldeas</t>
         </is>
       </c>
+      <c r="K614" t="inlineStr"/>
+      <c r="L614" t="inlineStr"/>
+      <c r="M614" t="inlineStr"/>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
@@ -22423,6 +24277,9 @@
           <t>Sentencia 265: Hijos de Elpaal: Heber, Misam y Semed, el cual edificó Ono, y Lod con sus aldeas</t>
         </is>
       </c>
+      <c r="K615" t="inlineStr"/>
+      <c r="L615" t="inlineStr"/>
+      <c r="M615" t="inlineStr"/>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
@@ -22457,6 +24314,9 @@
           <t>Sentencia 265: Hijos de Elpaal: Heber, Misam y Semed, el cual edificó Ono, y Lod con sus aldeas</t>
         </is>
       </c>
+      <c r="K616" t="inlineStr"/>
+      <c r="L616" t="inlineStr"/>
+      <c r="M616" t="inlineStr"/>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
@@ -22491,6 +24351,9 @@
           <t>Sentencia 265: Hijos de Elpaal: Heber, Misam y Semed, el cual edificó Ono, y Lod con sus aldeas</t>
         </is>
       </c>
+      <c r="K617" t="inlineStr"/>
+      <c r="L617" t="inlineStr"/>
+      <c r="M617" t="inlineStr"/>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
@@ -22523,6 +24386,9 @@
           <t>Sentencia 266: Linaje de Bería</t>
         </is>
       </c>
+      <c r="K618" t="inlineStr"/>
+      <c r="L618" t="inlineStr"/>
+      <c r="M618" t="inlineStr"/>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
@@ -22557,6 +24423,9 @@
           <t>Sentencia 266: Hijo de Sema</t>
         </is>
       </c>
+      <c r="K619" t="inlineStr"/>
+      <c r="L619" t="inlineStr"/>
+      <c r="M619" t="inlineStr"/>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
@@ -22591,6 +24460,9 @@
           <t>Sentencia 266: Hijo de Sema</t>
         </is>
       </c>
+      <c r="K620" t="inlineStr"/>
+      <c r="L620" t="inlineStr"/>
+      <c r="M620" t="inlineStr"/>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
@@ -22623,6 +24495,9 @@
           <t>Sentencia 274: Y Miclot engendró a Simea</t>
         </is>
       </c>
+      <c r="K621" t="inlineStr"/>
+      <c r="L621" t="inlineStr"/>
+      <c r="M621" t="inlineStr"/>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
@@ -22655,6 +24530,9 @@
           <t>Sentencia 275: Estos también habitaron con sus hermanos en Jerusalén es padre de enfrente de ellos</t>
         </is>
       </c>
+      <c r="K622" t="inlineStr"/>
+      <c r="L622" t="inlineStr"/>
+      <c r="M622" t="inlineStr"/>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
@@ -22687,6 +24565,9 @@
           <t>Sentencia 276: Ner engendró a Cis, Cis engendró a Saúl, y Saúl engendró a Jonatán, Malquisúa, Abinadab y Es-Baal</t>
         </is>
       </c>
+      <c r="K623" t="inlineStr"/>
+      <c r="L623" t="inlineStr"/>
+      <c r="M623" t="inlineStr"/>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
@@ -22719,6 +24600,9 @@
           <t>Sentencia 276: Ner engendró a Cis, Cis engendró a Saúl, y Saúl engendró a Jonatán, Malquisúa, Abinadab y Es-Baal</t>
         </is>
       </c>
+      <c r="K624" t="inlineStr"/>
+      <c r="L624" t="inlineStr"/>
+      <c r="M624" t="inlineStr"/>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
@@ -22751,6 +24635,9 @@
           <t>Sentencia 276: Ner engendró a Cis, Cis engendró a Saúl, y Saúl engendró a Jonatán, Malquisúa, Abinadab y Es-Baal</t>
         </is>
       </c>
+      <c r="K625" t="inlineStr"/>
+      <c r="L625" t="inlineStr"/>
+      <c r="M625" t="inlineStr"/>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
@@ -22783,6 +24670,9 @@
           <t>Sentencia 277: Hijo de Jonatán fue Merib-Baal, y Merib-Baal  engendró a Micaía</t>
         </is>
       </c>
+      <c r="K626" t="inlineStr"/>
+      <c r="L626" t="inlineStr"/>
+      <c r="M626" t="inlineStr"/>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
@@ -22817,6 +24707,9 @@
           <t>Sentencia 278: Los hijos de Micaía: Pitón, Melec, Tarea y Acaz</t>
         </is>
       </c>
+      <c r="K627" t="inlineStr"/>
+      <c r="L627" t="inlineStr"/>
+      <c r="M627" t="inlineStr"/>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
@@ -22851,6 +24744,9 @@
           <t>Sentencia 278: Los hijos de Micaía: Pitón, Melec, Tarea y Acaz</t>
         </is>
       </c>
+      <c r="K628" t="inlineStr"/>
+      <c r="L628" t="inlineStr"/>
+      <c r="M628" t="inlineStr"/>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
@@ -22885,6 +24781,9 @@
           <t>Sentencia 278: Los hijos de Micaía: Pitón, Melec, Tarea y Acaz</t>
         </is>
       </c>
+      <c r="K629" t="inlineStr"/>
+      <c r="L629" t="inlineStr"/>
+      <c r="M629" t="inlineStr"/>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
@@ -22919,6 +24818,9 @@
           <t>Sentencia 278: Los hijos de Micaía: Pitón, Melec, Tarea y Acaz</t>
         </is>
       </c>
+      <c r="K630" t="inlineStr"/>
+      <c r="L630" t="inlineStr"/>
+      <c r="M630" t="inlineStr"/>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
@@ -22951,6 +24853,9 @@
           <t>Sentencia 279: Acaz engendró a Joada, Joada engendró a Alemet, Azmavet y Zimri, y Zimri engendró a Mosa</t>
         </is>
       </c>
+      <c r="K631" t="inlineStr"/>
+      <c r="L631" t="inlineStr"/>
+      <c r="M631" t="inlineStr"/>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
@@ -22983,6 +24888,9 @@
           <t>Sentencia 279: Acaz engendró a Joada, Joada engendró a Alemet, Azmavet y Zimri, y Zimri engendró a Mosa</t>
         </is>
       </c>
+      <c r="K632" t="inlineStr"/>
+      <c r="L632" t="inlineStr"/>
+      <c r="M632" t="inlineStr"/>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
@@ -23015,6 +24923,9 @@
           <t>Sentencia 279: Acaz engendró a Joada, Joada engendró a Alemet, Azmavet y Zimri, y Zimri engendró a Mosa</t>
         </is>
       </c>
+      <c r="K633" t="inlineStr"/>
+      <c r="L633" t="inlineStr"/>
+      <c r="M633" t="inlineStr"/>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
@@ -23047,6 +24958,9 @@
           <t>Sentencia 280: Mosa engendró a Bina, hijo del cual fue Rafa, hijo del cual fue Elasa, cuyo hijo fue Azel</t>
         </is>
       </c>
+      <c r="K634" t="inlineStr"/>
+      <c r="L634" t="inlineStr"/>
+      <c r="M634" t="inlineStr"/>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
@@ -23081,6 +24995,9 @@
           <t>Sentencia 282: Y los hijos de Esec su hermano: Ulam su primogénito, Jehús el segundo, Elifelet el tercero</t>
         </is>
       </c>
+      <c r="K635" t="inlineStr"/>
+      <c r="L635" t="inlineStr"/>
+      <c r="M635" t="inlineStr"/>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
@@ -23115,6 +25032,9 @@
           <t>Sentencia 282: Y los hijos de Esec su hermano: Ulam su primogénito, Jehús el segundo, Elifelet el tercero</t>
         </is>
       </c>
+      <c r="K636" t="inlineStr"/>
+      <c r="L636" t="inlineStr"/>
+      <c r="M636" t="inlineStr"/>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
@@ -23149,6 +25069,9 @@
           <t>Sentencia 282: Y los hijos de Esec su hermano: Ulam su primogénito, Jehús el segundo, Elifelet el tercero</t>
         </is>
       </c>
+      <c r="K637" t="inlineStr"/>
+      <c r="L637" t="inlineStr"/>
+      <c r="M637" t="inlineStr"/>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
@@ -23183,6 +25106,9 @@
           <t>Sentencia 290: De los hijos de Zera: Jeuel y sus hermanos: seiscientos noventa</t>
         </is>
       </c>
+      <c r="K638" t="inlineStr"/>
+      <c r="L638" t="inlineStr"/>
+      <c r="M638" t="inlineStr"/>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
@@ -23217,6 +25143,9 @@
           <t>Sentencia 290: De los hijos de Zera: Jeuel y sus hermanos: seiscientos noventa</t>
         </is>
       </c>
+      <c r="K639" t="inlineStr"/>
+      <c r="L639" t="inlineStr"/>
+      <c r="M639" t="inlineStr"/>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -23263,6 +25192,9 @@
           <t>Sentencia 291: Y de los hijos de Benjamín: Salú ben Mesulam, hijo de Hodavías, hijo de Asenúa, Ibneías ben Jeroham,</t>
         </is>
       </c>
+      <c r="K640" t="inlineStr"/>
+      <c r="L640" t="inlineStr"/>
+      <c r="M640" t="inlineStr"/>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
@@ -23309,6 +25241,9 @@
           <t>Sentencia 291: Y de los hijos de Benjamín: Salú ben Mesulam, hijo de Hodavías, hijo de Asenúa, Ibneías ben Jeroham,</t>
         </is>
       </c>
+      <c r="K641" t="inlineStr"/>
+      <c r="L641" t="inlineStr"/>
+      <c r="M641" t="inlineStr"/>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
@@ -23355,6 +25290,9 @@
           <t>Sentencia 291: Y de los hijos de Benjamín: Salú ben Mesulam, hijo de Hodavías, hijo de Asenúa, Ibneías ben Jeroham,</t>
         </is>
       </c>
+      <c r="K642" t="inlineStr"/>
+      <c r="L642" t="inlineStr"/>
+      <c r="M642" t="inlineStr"/>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
@@ -23401,6 +25339,9 @@
           <t>Sentencia 291: Y de los hijos de Benjamín: Salú ben Mesulam, hijo de Hodavías, hijo de Asenúa, Ibneías ben Jeroham,</t>
         </is>
       </c>
+      <c r="K643" t="inlineStr"/>
+      <c r="L643" t="inlineStr"/>
+      <c r="M643" t="inlineStr"/>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
@@ -23435,6 +25376,9 @@
           <t>Sentencia 292: Hijo de sus hermanos por sus linajes: novecientos cincuenta</t>
         </is>
       </c>
+      <c r="K644" t="inlineStr"/>
+      <c r="L644" t="inlineStr"/>
+      <c r="M644" t="inlineStr"/>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
@@ -23471,6 +25415,9 @@
           <t xml:space="preserve">Sentencia 294: De los sacerdotes: Jedaías, Joiarib, Jaquín, y Azarías ben Hilcías, hijo de Mesulam, hijo de Sadoc, </t>
         </is>
       </c>
+      <c r="K645" t="inlineStr"/>
+      <c r="L645" t="inlineStr"/>
+      <c r="M645" t="inlineStr"/>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
@@ -23503,6 +25450,9 @@
           <t>Sentencia 296: Linaje de los porteros: Salum</t>
         </is>
       </c>
+      <c r="K646" t="inlineStr"/>
+      <c r="L646" t="inlineStr"/>
+      <c r="M646" t="inlineStr"/>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
@@ -23537,6 +25487,9 @@
           <t>Sentencia 296: Hijo de Acub</t>
         </is>
       </c>
+      <c r="K647" t="inlineStr"/>
+      <c r="L647" t="inlineStr"/>
+      <c r="M647" t="inlineStr"/>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
@@ -23571,6 +25524,9 @@
           <t>Sentencia 296: Hijo de Acub</t>
         </is>
       </c>
+      <c r="K648" t="inlineStr"/>
+      <c r="L648" t="inlineStr"/>
+      <c r="M648" t="inlineStr"/>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
@@ -23605,6 +25561,9 @@
           <t>Sentencia 297: Hijo de Hasta entonces estaban encargados de la puerta real</t>
         </is>
       </c>
+      <c r="K649" t="inlineStr"/>
+      <c r="L649" t="inlineStr"/>
+      <c r="M649" t="inlineStr"/>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
@@ -23639,6 +25598,9 @@
           <t>Sentencia 297: Hijo de Hasta entonces estaban encargados de la puerta real</t>
         </is>
       </c>
+      <c r="K650" t="inlineStr"/>
+      <c r="L650" t="inlineStr"/>
+      <c r="M650" t="inlineStr"/>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
@@ -23671,6 +25633,9 @@
           <t>Sentencia 299: Linaje de En tiempo antiguo</t>
         </is>
       </c>
+      <c r="K651" t="inlineStr"/>
+      <c r="L651" t="inlineStr"/>
+      <c r="M651" t="inlineStr"/>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
@@ -23705,6 +25670,9 @@
           <t>Sentencia 299: Hijo de Finees</t>
         </is>
       </c>
+      <c r="K652" t="inlineStr"/>
+      <c r="L652" t="inlineStr"/>
+      <c r="M652" t="inlineStr"/>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
@@ -23739,6 +25707,9 @@
           <t>Sentencia 299: Hijo de Finees</t>
         </is>
       </c>
+      <c r="K653" t="inlineStr"/>
+      <c r="L653" t="inlineStr"/>
+      <c r="M653" t="inlineStr"/>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
@@ -23783,6 +25754,9 @@
           <t>Hijos de Ismael — Ase.txt líneas 17-19 (corrección manual)</t>
         </is>
       </c>
+      <c r="K654" t="inlineStr"/>
+      <c r="L654" t="inlineStr"/>
+      <c r="M654" t="inlineStr"/>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
@@ -23827,6 +25801,9 @@
           <t>Hijos de Ismael — Ase.txt líneas 17-19 (corrección manual)</t>
         </is>
       </c>
+      <c r="K655" t="inlineStr"/>
+      <c r="L655" t="inlineStr"/>
+      <c r="M655" t="inlineStr"/>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
@@ -23871,6 +25848,9 @@
           <t>Hijos de Ismael — Ase.txt líneas 17-19 (corrección manual)</t>
         </is>
       </c>
+      <c r="K656" t="inlineStr"/>
+      <c r="L656" t="inlineStr"/>
+      <c r="M656" t="inlineStr"/>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
@@ -23915,6 +25895,9 @@
           <t>Hijos de Ismael — Ase.txt líneas 17-19 (corrección manual)</t>
         </is>
       </c>
+      <c r="K657" t="inlineStr"/>
+      <c r="L657" t="inlineStr"/>
+      <c r="M657" t="inlineStr"/>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
@@ -23959,6 +25942,9 @@
           <t>Hijos de Ismael — Ase.txt líneas 17-19 (corrección manual)</t>
         </is>
       </c>
+      <c r="K658" t="inlineStr"/>
+      <c r="L658" t="inlineStr"/>
+      <c r="M658" t="inlineStr"/>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
@@ -24003,6 +25989,9 @@
           <t>Hijos de Ismael — Ase.txt líneas 17-19 (corrección manual)</t>
         </is>
       </c>
+      <c r="K659" t="inlineStr"/>
+      <c r="L659" t="inlineStr"/>
+      <c r="M659" t="inlineStr"/>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
@@ -24047,6 +26036,9 @@
           <t>Hijos de Ismael — Ase.txt líneas 17-19 (corrección manual)</t>
         </is>
       </c>
+      <c r="K660" t="inlineStr"/>
+      <c r="L660" t="inlineStr"/>
+      <c r="M660" t="inlineStr"/>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
@@ -24091,6 +26083,9 @@
           <t>Hijos de Ismael — Ase.txt líneas 17-19 (corrección manual)</t>
         </is>
       </c>
+      <c r="K661" t="inlineStr"/>
+      <c r="L661" t="inlineStr"/>
+      <c r="M661" t="inlineStr"/>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
@@ -24135,6 +26130,9 @@
           <t>Hijos de Ismael — Ase.txt líneas 17-19 (corrección manual)</t>
         </is>
       </c>
+      <c r="K662" t="inlineStr"/>
+      <c r="L662" t="inlineStr"/>
+      <c r="M662" t="inlineStr"/>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
@@ -24179,6 +26177,9 @@
           <t>Hijos de Ismael — Ase.txt líneas 17-19 (corrección manual)</t>
         </is>
       </c>
+      <c r="K663" t="inlineStr"/>
+      <c r="L663" t="inlineStr"/>
+      <c r="M663" t="inlineStr"/>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
@@ -24223,6 +26224,9 @@
           <t>Hijos de Ismael — Ase.txt líneas 17-19 (corrección manual)</t>
         </is>
       </c>
+      <c r="K664" t="inlineStr"/>
+      <c r="L664" t="inlineStr"/>
+      <c r="M664" t="inlineStr"/>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
@@ -24267,6 +26271,9 @@
           <t>Hijos de Ismael — Ase.txt líneas 17-19 (corrección manual)</t>
         </is>
       </c>
+      <c r="K665" t="inlineStr"/>
+      <c r="L665" t="inlineStr"/>
+      <c r="M665" t="inlineStr"/>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
@@ -24315,6 +26322,9 @@
           <t>Hijo de Abraham y Cetura — Ase.txt línea 20 (corrección manual)</t>
         </is>
       </c>
+      <c r="K666" t="inlineStr"/>
+      <c r="L666" t="inlineStr"/>
+      <c r="M666" t="inlineStr"/>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
@@ -24363,6 +26373,9 @@
           <t>Hijo de Abraham y Cetura — Ase.txt línea 20 (corrección manual)</t>
         </is>
       </c>
+      <c r="K667" t="inlineStr"/>
+      <c r="L667" t="inlineStr"/>
+      <c r="M667" t="inlineStr"/>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
@@ -24411,6 +26424,9 @@
           <t>Hijo de Abraham y Cetura — Ase.txt línea 20 (corrección manual)</t>
         </is>
       </c>
+      <c r="K668" t="inlineStr"/>
+      <c r="L668" t="inlineStr"/>
+      <c r="M668" t="inlineStr"/>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
@@ -24459,6 +26475,9 @@
           <t>Hijo de Abraham y Cetura — Ase.txt línea 20 (corrección manual)</t>
         </is>
       </c>
+      <c r="K669" t="inlineStr"/>
+      <c r="L669" t="inlineStr"/>
+      <c r="M669" t="inlineStr"/>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
@@ -24507,6 +26526,9 @@
           <t>Hijo de Elifaz con su concubina Timna — Ase.txt línea 24 (corrección: sustituye fila 'de Timna')</t>
         </is>
       </c>
+      <c r="K670" t="inlineStr"/>
+      <c r="L670" t="inlineStr"/>
+      <c r="M670" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
